--- a/research/traditional_assets/database/data/greece/greece_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_drugs_pharmaceutical.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1136355261009444</v>
+        <v>0.1134206279435223</v>
       </c>
       <c r="C2">
-        <v>173.2197991483275</v>
+        <v>172.0167040096342</v>
       </c>
       <c r="D2">
-        <v>163.9097991483275</v>
+        <v>164.4307040096342</v>
       </c>
       <c r="E2">
-        <v>-33.6</v>
+        <v>-31.876</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.724</v>
       </c>
       <c r="G2">
         <v>9.31</v>
@@ -1445,28 +1445,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08671720000000001</v>
       </c>
       <c r="N2">
-        <v>6.366666666666666</v>
+        <v>6.279949466666666</v>
       </c>
       <c r="O2">
-        <v>1.400666666666667</v>
+        <v>1.381588882666667</v>
       </c>
       <c r="P2">
-        <v>4.965999999999999</v>
+        <v>4.898360584</v>
       </c>
       <c r="Q2">
-        <v>8.745999999999999</v>
+        <v>8.678360584</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1136355261009444</v>
+        <v>0.1141699878217397</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286288</v>
+        <v>0.8910901381273998</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>73.41872969453195</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1134206279435223</v>
+        <v>0.1132057297861002</v>
       </c>
       <c r="C3">
-        <v>172.0167040096342</v>
+        <v>170.816930294661</v>
       </c>
       <c r="D3">
-        <v>164.4307040096342</v>
+        <v>164.954930294661</v>
       </c>
       <c r="E3">
-        <v>-31.876</v>
+        <v>-30.152</v>
       </c>
       <c r="F3">
-        <v>1.724</v>
+        <v>3.448</v>
       </c>
       <c r="G3">
         <v>9.31</v>
@@ -1527,28 +1527,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M3">
-        <v>0.08671720000000001</v>
+        <v>0.1734344</v>
       </c>
       <c r="N3">
-        <v>6.279949466666666</v>
+        <v>6.193232266666667</v>
       </c>
       <c r="O3">
-        <v>1.381588882666667</v>
+        <v>1.362511098666667</v>
       </c>
       <c r="P3">
-        <v>4.898360584</v>
+        <v>4.830721168</v>
       </c>
       <c r="Q3">
-        <v>8.678360584</v>
+        <v>8.610721168000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1141699878217397</v>
+        <v>0.1147153569245921</v>
       </c>
       <c r="T3">
-        <v>0.8910901381273998</v>
+        <v>0.898198125779207</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>73.41872969453195</v>
+        <v>36.70936484726597</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1132057297861002</v>
+        <v>0.1129908316286782</v>
       </c>
       <c r="C4">
-        <v>170.816930294661</v>
+        <v>169.6205098723914</v>
       </c>
       <c r="D4">
-        <v>164.954930294661</v>
+        <v>165.4825098723913</v>
       </c>
       <c r="E4">
-        <v>-30.152</v>
+        <v>-28.428</v>
       </c>
       <c r="F4">
-        <v>3.448</v>
+        <v>5.172</v>
       </c>
       <c r="G4">
         <v>9.31</v>
@@ -1609,28 +1609,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M4">
-        <v>0.1734344</v>
+        <v>0.2601516</v>
       </c>
       <c r="N4">
-        <v>6.193232266666667</v>
+        <v>6.106515066666666</v>
       </c>
       <c r="O4">
-        <v>1.362511098666667</v>
+        <v>1.343433314666667</v>
       </c>
       <c r="P4">
-        <v>4.830721168</v>
+        <v>4.763081752</v>
       </c>
       <c r="Q4">
-        <v>8.610721168000001</v>
+        <v>8.543081751999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1147153569245921</v>
+        <v>0.1152719707512146</v>
       </c>
       <c r="T4">
-        <v>0.898198125779207</v>
+        <v>0.9054526698774431</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.70936484726597</v>
+        <v>24.47290989817732</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1129908316286782</v>
+        <v>0.1127759334712561</v>
       </c>
       <c r="C5">
-        <v>169.6205098723914</v>
+        <v>168.4274750208266</v>
       </c>
       <c r="D5">
-        <v>165.4825098723913</v>
+        <v>166.0134750208266</v>
       </c>
       <c r="E5">
-        <v>-28.428</v>
+        <v>-26.704</v>
       </c>
       <c r="F5">
-        <v>5.172</v>
+        <v>6.896000000000001</v>
       </c>
       <c r="G5">
         <v>9.31</v>
@@ -1691,28 +1691,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M5">
-        <v>0.2601516</v>
+        <v>0.3468688</v>
       </c>
       <c r="N5">
-        <v>6.106515066666666</v>
+        <v>6.019797866666666</v>
       </c>
       <c r="O5">
-        <v>1.343433314666667</v>
+        <v>1.324355530666667</v>
       </c>
       <c r="P5">
-        <v>4.763081752</v>
+        <v>4.695442335999999</v>
       </c>
       <c r="Q5">
-        <v>8.543081751999999</v>
+        <v>8.475442336</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1152719707512146</v>
+        <v>0.1158401806992251</v>
       </c>
       <c r="T5">
-        <v>0.9054526698774431</v>
+        <v>0.9128583503110592</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.47290989817732</v>
+        <v>18.35468242363299</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1127759334712561</v>
+        <v>0.112561035313834</v>
       </c>
       <c r="C6">
-        <v>168.4274750208266</v>
+        <v>167.2378584335688</v>
       </c>
       <c r="D6">
-        <v>166.0134750208266</v>
+        <v>166.5478584335688</v>
       </c>
       <c r="E6">
-        <v>-26.704</v>
+        <v>-24.98</v>
       </c>
       <c r="F6">
-        <v>6.896000000000001</v>
+        <v>8.620000000000001</v>
       </c>
       <c r="G6">
         <v>9.31</v>
@@ -1773,28 +1773,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M6">
-        <v>0.3468688</v>
+        <v>0.433586</v>
       </c>
       <c r="N6">
-        <v>6.019797866666666</v>
+        <v>5.933080666666666</v>
       </c>
       <c r="O6">
-        <v>1.324355530666667</v>
+        <v>1.305277746666667</v>
       </c>
       <c r="P6">
-        <v>4.695442335999999</v>
+        <v>4.62780292</v>
       </c>
       <c r="Q6">
-        <v>8.475442336</v>
+        <v>8.40780292</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1158401806992251</v>
+        <v>0.1164203529619306</v>
       </c>
       <c r="T6">
-        <v>0.9128583503110592</v>
+        <v>0.9204199398064358</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.35468242363299</v>
+        <v>14.68374593890639</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.112561035313834</v>
+        <v>0.1124163371564119</v>
       </c>
       <c r="C7">
-        <v>167.2378584335688</v>
+        <v>165.8756190656695</v>
       </c>
       <c r="D7">
-        <v>166.5478584335688</v>
+        <v>166.9096190656695</v>
       </c>
       <c r="E7">
-        <v>-24.98</v>
+        <v>-23.256</v>
       </c>
       <c r="F7">
-        <v>8.620000000000001</v>
+        <v>10.344</v>
       </c>
       <c r="G7">
         <v>9.31</v>
@@ -1855,45 +1855,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M7">
-        <v>0.433586</v>
+        <v>0.5358192000000001</v>
       </c>
       <c r="N7">
-        <v>5.933080666666666</v>
+        <v>5.830847466666667</v>
       </c>
       <c r="O7">
-        <v>1.305277746666667</v>
+        <v>1.282786442666667</v>
       </c>
       <c r="P7">
-        <v>4.62780292</v>
+        <v>4.548061024</v>
       </c>
       <c r="Q7">
-        <v>8.40780292</v>
+        <v>8.328061024</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1164203529619306</v>
+        <v>0.1170128693153319</v>
       </c>
       <c r="T7">
-        <v>0.9204199398064358</v>
+        <v>0.9281424141846925</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.68374593890639</v>
+        <v>11.88211745056292</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1124163371564119</v>
+        <v>0.1122131389989899</v>
       </c>
       <c r="C8">
-        <v>165.8756190656695</v>
+        <v>164.6622970363446</v>
       </c>
       <c r="D8">
-        <v>166.9096190656695</v>
+        <v>167.4202970363446</v>
       </c>
       <c r="E8">
-        <v>-23.256</v>
+        <v>-21.532</v>
       </c>
       <c r="F8">
-        <v>10.344</v>
+        <v>12.068</v>
       </c>
       <c r="G8">
         <v>9.31</v>
@@ -1937,28 +1937,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M8">
-        <v>0.5358191999999999</v>
+        <v>0.6251224</v>
       </c>
       <c r="N8">
-        <v>5.830847466666667</v>
+        <v>5.741544266666667</v>
       </c>
       <c r="O8">
-        <v>1.282786442666667</v>
+        <v>1.263139738666667</v>
       </c>
       <c r="P8">
-        <v>4.548061024</v>
+        <v>4.478404528</v>
       </c>
       <c r="Q8">
-        <v>8.328061024</v>
+        <v>8.258404528</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1170128693153319</v>
+        <v>0.1176181279559031</v>
       </c>
       <c r="T8">
-        <v>0.9281424141846925</v>
+        <v>0.9360309632807611</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.88211745056293</v>
+        <v>10.18467210048251</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1122131389989899</v>
+        <v>0.1121160208415678</v>
       </c>
       <c r="C9">
-        <v>164.6622970363445</v>
+        <v>163.183479882916</v>
       </c>
       <c r="D9">
-        <v>167.4202970363445</v>
+        <v>167.665479882916</v>
       </c>
       <c r="E9">
-        <v>-21.532</v>
+        <v>-19.808</v>
       </c>
       <c r="F9">
-        <v>12.068</v>
+        <v>13.792</v>
       </c>
       <c r="G9">
         <v>9.31</v>
@@ -2019,45 +2019,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M9">
-        <v>0.6251224000000001</v>
+        <v>0.7378720000000001</v>
       </c>
       <c r="N9">
-        <v>5.741544266666666</v>
+        <v>5.628794666666666</v>
       </c>
       <c r="O9">
-        <v>1.263139738666667</v>
+        <v>1.238334826666666</v>
       </c>
       <c r="P9">
-        <v>4.478404528</v>
+        <v>4.390459839999999</v>
       </c>
       <c r="Q9">
-        <v>8.258404528</v>
+        <v>8.170459839999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1176181279559031</v>
+        <v>0.1182365443930085</v>
       </c>
       <c r="T9">
-        <v>0.9360309632807613</v>
+        <v>0.9440910025745706</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.1846721004825</v>
+        <v>8.628416129988217</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1121160208415678</v>
+        <v>0.1119260826841457</v>
       </c>
       <c r="C10">
-        <v>163.183479882916</v>
+        <v>161.9410761157424</v>
       </c>
       <c r="D10">
-        <v>167.665479882916</v>
+        <v>168.1470761157424</v>
       </c>
       <c r="E10">
-        <v>-19.808</v>
+        <v>-18.084</v>
       </c>
       <c r="F10">
-        <v>13.792</v>
+        <v>15.516</v>
       </c>
       <c r="G10">
         <v>9.31</v>
@@ -2101,28 +2101,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M10">
-        <v>0.7378720000000001</v>
+        <v>0.830106</v>
       </c>
       <c r="N10">
-        <v>5.628794666666666</v>
+        <v>5.536560666666666</v>
       </c>
       <c r="O10">
-        <v>1.238334826666666</v>
+        <v>1.218043346666667</v>
       </c>
       <c r="P10">
-        <v>4.390459839999999</v>
+        <v>4.31851732</v>
       </c>
       <c r="Q10">
-        <v>8.170459839999999</v>
+        <v>8.098517319999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1182365443930085</v>
+        <v>0.1188685524001601</v>
       </c>
       <c r="T10">
-        <v>0.9440910025745706</v>
+        <v>0.952328185589123</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.628416129988217</v>
+        <v>7.669703226656194</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1119260826841457</v>
+        <v>0.1117985445267237</v>
       </c>
       <c r="C11">
-        <v>161.9410761157424</v>
+        <v>160.5420100732636</v>
       </c>
       <c r="D11">
-        <v>168.1470761157424</v>
+        <v>168.4720100732636</v>
       </c>
       <c r="E11">
-        <v>-18.084</v>
+        <v>-16.36</v>
       </c>
       <c r="F11">
-        <v>15.516</v>
+        <v>17.24</v>
       </c>
       <c r="G11">
         <v>9.31</v>
@@ -2183,45 +2183,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M11">
-        <v>0.830106</v>
+        <v>0.936132</v>
       </c>
       <c r="N11">
-        <v>5.536560666666666</v>
+        <v>5.430534666666667</v>
       </c>
       <c r="O11">
-        <v>1.218043346666667</v>
+        <v>1.194717626666667</v>
       </c>
       <c r="P11">
-        <v>4.31851732</v>
+        <v>4.23581704</v>
       </c>
       <c r="Q11">
-        <v>8.098517319999999</v>
+        <v>8.01581704</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1188685524001601</v>
+        <v>0.1195146050296929</v>
       </c>
       <c r="T11">
-        <v>0.952328185589123</v>
+        <v>0.9607484171151099</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.669703226656194</v>
+        <v>6.801035181648172</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1117985445267237</v>
+        <v>0.1116148463693016</v>
       </c>
       <c r="C12">
-        <v>160.5420100732636</v>
+        <v>159.2882382897666</v>
       </c>
       <c r="D12">
-        <v>168.4720100732636</v>
+        <v>168.9422382897665</v>
       </c>
       <c r="E12">
-        <v>-16.36</v>
+        <v>-14.636</v>
       </c>
       <c r="F12">
-        <v>17.24</v>
+        <v>18.964</v>
       </c>
       <c r="G12">
         <v>9.31</v>
@@ -2265,28 +2265,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M12">
-        <v>0.9361320000000001</v>
+        <v>1.0297452</v>
       </c>
       <c r="N12">
-        <v>5.430534666666667</v>
+        <v>5.336921466666666</v>
       </c>
       <c r="O12">
-        <v>1.194717626666667</v>
+        <v>1.174122722666667</v>
       </c>
       <c r="P12">
-        <v>4.23581704</v>
+        <v>4.162798744</v>
       </c>
       <c r="Q12">
-        <v>8.01581704</v>
+        <v>7.942798744</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1195146050296929</v>
+        <v>0.1201751756958445</v>
       </c>
       <c r="T12">
-        <v>0.9607484171151099</v>
+        <v>0.9693578673270743</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.801035181648172</v>
+        <v>6.182759256043791</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1116148463693016</v>
+        <v>0.1115247482118795</v>
       </c>
       <c r="C13">
-        <v>159.2882382897666</v>
+        <v>157.7958311797324</v>
       </c>
       <c r="D13">
-        <v>168.9422382897665</v>
+        <v>169.1738311797324</v>
       </c>
       <c r="E13">
-        <v>-14.636</v>
+        <v>-12.912</v>
       </c>
       <c r="F13">
-        <v>18.964</v>
+        <v>20.688</v>
       </c>
       <c r="G13">
         <v>9.31</v>
@@ -2347,45 +2347,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M13">
-        <v>1.0297452</v>
+        <v>1.1440464</v>
       </c>
       <c r="N13">
-        <v>5.336921466666666</v>
+        <v>5.222620266666667</v>
       </c>
       <c r="O13">
-        <v>1.174122722666667</v>
+        <v>1.148976458666667</v>
       </c>
       <c r="P13">
-        <v>4.162798744</v>
+        <v>4.073643808</v>
       </c>
       <c r="Q13">
-        <v>7.942798744</v>
+        <v>7.853643808</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1201751756958445</v>
+        <v>0.1208507593316812</v>
       </c>
       <c r="T13">
-        <v>0.9693578673270743</v>
+        <v>0.9781629868620376</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.182759256043791</v>
+        <v>5.565042350263649</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1115247482118795</v>
+        <v>0.1113488500544574</v>
       </c>
       <c r="C14">
-        <v>157.7958311797324</v>
+        <v>156.525803524996</v>
       </c>
       <c r="D14">
-        <v>169.1738311797324</v>
+        <v>169.627803524996</v>
       </c>
       <c r="E14">
-        <v>-12.912</v>
+        <v>-11.188</v>
       </c>
       <c r="F14">
-        <v>20.688</v>
+        <v>22.412</v>
       </c>
       <c r="G14">
         <v>9.31</v>
@@ -2429,28 +2429,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M14">
-        <v>1.1440464</v>
+        <v>1.2393836</v>
       </c>
       <c r="N14">
-        <v>5.222620266666667</v>
+        <v>5.127283066666666</v>
       </c>
       <c r="O14">
-        <v>1.148976458666667</v>
+        <v>1.128002274666666</v>
       </c>
       <c r="P14">
-        <v>4.073643808</v>
+        <v>3.999280792</v>
       </c>
       <c r="Q14">
-        <v>7.853643808</v>
+        <v>7.779280792</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1208507593316812</v>
+        <v>0.1215418736258131</v>
       </c>
       <c r="T14">
-        <v>0.9781629868620376</v>
+        <v>0.9871705229380345</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.565042350263649</v>
+        <v>5.136962169474137</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1113488500544574</v>
+        <v>0.1111729518970353</v>
       </c>
       <c r="C15">
-        <v>156.525803524996</v>
+        <v>155.2582188653128</v>
       </c>
       <c r="D15">
-        <v>169.627803524996</v>
+        <v>170.0842188653128</v>
       </c>
       <c r="E15">
-        <v>-11.188</v>
+        <v>-9.463999999999999</v>
       </c>
       <c r="F15">
-        <v>22.412</v>
+        <v>24.136</v>
       </c>
       <c r="G15">
         <v>9.31</v>
@@ -2511,28 +2511,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M15">
-        <v>1.2393836</v>
+        <v>1.3347208</v>
       </c>
       <c r="N15">
-        <v>5.127283066666666</v>
+        <v>5.031945866666666</v>
       </c>
       <c r="O15">
-        <v>1.128002274666666</v>
+        <v>1.107028090666667</v>
       </c>
       <c r="P15">
-        <v>3.999280792</v>
+        <v>3.924917775999999</v>
       </c>
       <c r="Q15">
-        <v>7.779280792</v>
+        <v>7.704917775999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1215418736258131</v>
+        <v>0.1222490603453899</v>
       </c>
       <c r="T15">
-        <v>0.9871705229380345</v>
+        <v>0.9963875365971943</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.136962169474137</v>
+        <v>4.770036300225984</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1111729518970353</v>
+        <v>0.1112895537396133</v>
       </c>
       <c r="C16">
-        <v>155.2582188653128</v>
+        <v>153.2313899074003</v>
       </c>
       <c r="D16">
-        <v>170.0842188653128</v>
+        <v>169.7813899074003</v>
       </c>
       <c r="E16">
-        <v>-9.463999999999999</v>
+        <v>-7.739999999999998</v>
       </c>
       <c r="F16">
-        <v>24.136</v>
+        <v>25.86</v>
       </c>
       <c r="G16">
         <v>9.31</v>
@@ -2593,45 +2593,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M16">
-        <v>1.3347208</v>
+        <v>1.494708</v>
       </c>
       <c r="N16">
-        <v>5.031945866666666</v>
+        <v>4.871958666666666</v>
       </c>
       <c r="O16">
-        <v>1.107028090666667</v>
+        <v>1.071830906666666</v>
       </c>
       <c r="P16">
-        <v>3.924917775999999</v>
+        <v>3.80012776</v>
       </c>
       <c r="Q16">
-        <v>7.704917775999999</v>
+        <v>7.58012776</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1222490603453899</v>
+        <v>0.1229728867524862</v>
       </c>
       <c r="T16">
-        <v>0.9963875365971943</v>
+        <v>1.005821421165981</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.770036300225984</v>
+        <v>4.259471861170653</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1112895537396132</v>
+        <v>0.1115699555821912</v>
       </c>
       <c r="C17">
-        <v>153.2313899074003</v>
+        <v>150.7835485402584</v>
       </c>
       <c r="D17">
-        <v>169.7813899074003</v>
+        <v>169.0575485402584</v>
       </c>
       <c r="E17">
-        <v>-7.740000000000002</v>
+        <v>-6.015999999999998</v>
       </c>
       <c r="F17">
-        <v>25.86</v>
+        <v>27.584</v>
       </c>
       <c r="G17">
         <v>9.31</v>
@@ -2675,45 +2675,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M17">
-        <v>1.494708</v>
+        <v>1.6908992</v>
       </c>
       <c r="N17">
-        <v>4.871958666666666</v>
+        <v>4.675767466666666</v>
       </c>
       <c r="O17">
-        <v>1.071830906666666</v>
+        <v>1.028668842666667</v>
       </c>
       <c r="P17">
-        <v>3.80012776</v>
+        <v>3.647098623999999</v>
       </c>
       <c r="Q17">
-        <v>7.58012776</v>
+        <v>7.427098623999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1229728867524862</v>
+        <v>0.1237139471216561</v>
       </c>
       <c r="T17">
-        <v>1.005821421165981</v>
+        <v>1.015479922034025</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.259471861170654</v>
+        <v>3.76525499962781</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1115699555821912</v>
+        <v>0.1114408574247691</v>
       </c>
       <c r="C18">
-        <v>150.7835485402584</v>
+        <v>149.3920399011437</v>
       </c>
       <c r="D18">
-        <v>169.0575485402584</v>
+        <v>169.3900399011437</v>
       </c>
       <c r="E18">
-        <v>-6.015999999999998</v>
+        <v>-4.291999999999998</v>
       </c>
       <c r="F18">
-        <v>27.584</v>
+        <v>29.308</v>
       </c>
       <c r="G18">
         <v>9.31</v>
@@ -2757,28 +2757,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M18">
-        <v>1.6908992</v>
+        <v>1.7965804</v>
       </c>
       <c r="N18">
-        <v>4.675767466666666</v>
+        <v>4.570086266666666</v>
       </c>
       <c r="O18">
-        <v>1.028668842666667</v>
+        <v>1.005418978666667</v>
       </c>
       <c r="P18">
-        <v>3.647098623999999</v>
+        <v>3.564667287999999</v>
       </c>
       <c r="Q18">
-        <v>7.427098623999999</v>
+        <v>7.344667287999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1237139471216561</v>
+        <v>0.1244728643671917</v>
       </c>
       <c r="T18">
-        <v>1.015479922034025</v>
+        <v>1.025371157862745</v>
       </c>
       <c r="U18">
         <v>0.0613</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.76525499962781</v>
+        <v>3.54376941141441</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1114408574247691</v>
+        <v>0.111704879267347</v>
       </c>
       <c r="C19">
-        <v>149.3920399011437</v>
+        <v>146.9894456764638</v>
       </c>
       <c r="D19">
-        <v>169.3900399011437</v>
+        <v>168.7114456764638</v>
       </c>
       <c r="E19">
-        <v>-4.291999999999998</v>
+        <v>-2.567999999999998</v>
       </c>
       <c r="F19">
-        <v>29.308</v>
+        <v>31.032</v>
       </c>
       <c r="G19">
         <v>9.31</v>
@@ -2839,45 +2839,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M19">
-        <v>1.7965804</v>
+        <v>1.9891512</v>
       </c>
       <c r="N19">
-        <v>4.570086266666666</v>
+        <v>4.377515466666666</v>
       </c>
       <c r="O19">
-        <v>1.005418978666667</v>
+        <v>0.9630534026666665</v>
       </c>
       <c r="P19">
-        <v>3.564667287999999</v>
+        <v>3.414462063999999</v>
       </c>
       <c r="Q19">
-        <v>7.344667287999999</v>
+        <v>7.194462064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1244728643671917</v>
+        <v>0.1252502917894476</v>
       </c>
       <c r="T19">
-        <v>1.025371157862745</v>
+        <v>1.035503643345823</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.54376941141441</v>
+        <v>3.200695184291001</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.111704879267347</v>
+        <v>0.1115976211099249</v>
       </c>
       <c r="C20">
-        <v>146.9894456764638</v>
+        <v>145.5404659354644</v>
       </c>
       <c r="D20">
-        <v>168.7114456764638</v>
+        <v>168.9864659354644</v>
       </c>
       <c r="E20">
-        <v>-2.568000000000001</v>
+        <v>-0.8440000000000012</v>
       </c>
       <c r="F20">
-        <v>31.032</v>
+        <v>32.756</v>
       </c>
       <c r="G20">
         <v>9.31</v>
@@ -2921,28 +2921,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M20">
-        <v>1.9891512</v>
+        <v>2.0996596</v>
       </c>
       <c r="N20">
-        <v>4.377515466666666</v>
+        <v>4.267007066666666</v>
       </c>
       <c r="O20">
-        <v>0.9630534026666665</v>
+        <v>0.9387415546666666</v>
       </c>
       <c r="P20">
-        <v>3.414462063999999</v>
+        <v>3.328265512</v>
       </c>
       <c r="Q20">
-        <v>7.194462064</v>
+        <v>7.108265512</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1252502917894476</v>
+        <v>0.1260469149505246</v>
       </c>
       <c r="T20">
-        <v>1.035503643345823</v>
+        <v>1.045886313655645</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.200695184291001</v>
+        <v>3.032237543012527</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1115976211099249</v>
+        <v>0.1127071629525029</v>
       </c>
       <c r="C21">
-        <v>145.5404659354644</v>
+        <v>141.0141119495709</v>
       </c>
       <c r="D21">
-        <v>168.9864659354644</v>
+        <v>166.1841119495709</v>
       </c>
       <c r="E21">
-        <v>-0.8440000000000012</v>
+        <v>0.8800000000000026</v>
       </c>
       <c r="F21">
-        <v>32.756</v>
+        <v>34.48</v>
       </c>
       <c r="G21">
         <v>9.31</v>
@@ -3003,45 +3003,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M21">
-        <v>2.0996596</v>
+        <v>2.479112000000001</v>
       </c>
       <c r="N21">
-        <v>4.267007066666666</v>
+        <v>3.887554666666666</v>
       </c>
       <c r="O21">
-        <v>0.9387415546666666</v>
+        <v>0.8552620266666664</v>
       </c>
       <c r="P21">
-        <v>3.328265512</v>
+        <v>3.032292639999999</v>
       </c>
       <c r="Q21">
-        <v>7.108265512</v>
+        <v>6.812292639999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1260469149505246</v>
+        <v>0.1268634536906286</v>
       </c>
       <c r="T21">
-        <v>1.045886313655645</v>
+        <v>1.056528550723211</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.032237543012527</v>
+        <v>2.568123855100804</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1127071629525029</v>
+        <v>0.1132995647950808</v>
       </c>
       <c r="C22">
-        <v>141.0141119495709</v>
+        <v>137.8316170033446</v>
       </c>
       <c r="D22">
-        <v>166.1841119495709</v>
+        <v>164.7256170033446</v>
       </c>
       <c r="E22">
-        <v>0.8800000000000026</v>
+        <v>2.604000000000006</v>
       </c>
       <c r="F22">
-        <v>34.48</v>
+        <v>36.20400000000001</v>
       </c>
       <c r="G22">
         <v>9.31</v>
@@ -3085,45 +3085,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M22">
-        <v>2.479112000000001</v>
+        <v>2.744263200000001</v>
       </c>
       <c r="N22">
-        <v>3.887554666666666</v>
+        <v>3.622403466666666</v>
       </c>
       <c r="O22">
-        <v>0.8552620266666664</v>
+        <v>0.7969287626666665</v>
       </c>
       <c r="P22">
-        <v>3.032292639999999</v>
+        <v>2.825474703999999</v>
       </c>
       <c r="Q22">
-        <v>6.812292639999999</v>
+        <v>6.605474703999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1268634536906286</v>
+        <v>0.1277006642975706</v>
       </c>
       <c r="T22">
-        <v>1.056528550723211</v>
+        <v>1.067440211514008</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.568123855100804</v>
+        <v>2.319991270030755</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1132995647950808</v>
+        <v>0.1132835666376587</v>
       </c>
       <c r="C23">
-        <v>137.8316170033446</v>
+        <v>136.1466680862019</v>
       </c>
       <c r="D23">
-        <v>164.7256170033446</v>
+        <v>164.7646680862019</v>
       </c>
       <c r="E23">
-        <v>2.603999999999999</v>
+        <v>4.328000000000003</v>
       </c>
       <c r="F23">
-        <v>36.204</v>
+        <v>37.928</v>
       </c>
       <c r="G23">
         <v>9.31</v>
@@ -3167,28 +3167,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M23">
-        <v>2.7442632</v>
+        <v>2.874942400000001</v>
       </c>
       <c r="N23">
-        <v>3.622403466666666</v>
+        <v>3.491724266666666</v>
       </c>
       <c r="O23">
-        <v>0.7969287626666666</v>
+        <v>0.7681793386666664</v>
       </c>
       <c r="P23">
-        <v>2.825474703999999</v>
+        <v>2.723544927999999</v>
       </c>
       <c r="Q23">
-        <v>6.605474704</v>
+        <v>6.503544927999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1277006642975706</v>
+        <v>0.1285593418431522</v>
       </c>
       <c r="T23">
-        <v>1.067440211514008</v>
+        <v>1.078631658478927</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.319991270030756</v>
+        <v>2.214537121392994</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1132835666376587</v>
+        <v>0.1132675684802366</v>
       </c>
       <c r="C24">
-        <v>136.1466680862019</v>
+        <v>134.4617376889312</v>
       </c>
       <c r="D24">
-        <v>164.7646680862019</v>
+        <v>164.8037376889312</v>
       </c>
       <c r="E24">
-        <v>4.328000000000003</v>
+        <v>6.052</v>
       </c>
       <c r="F24">
-        <v>37.928</v>
+        <v>39.652</v>
       </c>
       <c r="G24">
         <v>9.31</v>
@@ -3249,28 +3249,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M24">
-        <v>2.874942400000001</v>
+        <v>3.0056216</v>
       </c>
       <c r="N24">
-        <v>3.491724266666666</v>
+        <v>3.361045066666666</v>
       </c>
       <c r="O24">
-        <v>0.7681793386666664</v>
+        <v>0.7394299146666665</v>
       </c>
       <c r="P24">
-        <v>2.723544927999999</v>
+        <v>2.621615152</v>
       </c>
       <c r="Q24">
-        <v>6.503544927999999</v>
+        <v>6.401615152</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1285593418431522</v>
+        <v>0.129440322701606</v>
       </c>
       <c r="T24">
-        <v>1.078631658478927</v>
+        <v>1.090113792378</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.214537121392994</v>
+        <v>2.118252898723733</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1132675684802366</v>
+        <v>0.1132515703228145</v>
       </c>
       <c r="C25">
-        <v>134.4617376889312</v>
+        <v>132.7768258247104</v>
       </c>
       <c r="D25">
-        <v>164.8037376889312</v>
+        <v>164.8428258247104</v>
       </c>
       <c r="E25">
-        <v>6.052</v>
+        <v>7.776000000000003</v>
       </c>
       <c r="F25">
-        <v>39.652</v>
+        <v>41.376</v>
       </c>
       <c r="G25">
         <v>9.31</v>
@@ -3331,28 +3331,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M25">
-        <v>3.0056216</v>
+        <v>3.136300800000001</v>
       </c>
       <c r="N25">
-        <v>3.361045066666666</v>
+        <v>3.230365866666665</v>
       </c>
       <c r="O25">
-        <v>0.7394299146666665</v>
+        <v>0.7106804906666664</v>
       </c>
       <c r="P25">
-        <v>2.621615152</v>
+        <v>2.519685375999999</v>
       </c>
       <c r="Q25">
-        <v>6.401615152</v>
+        <v>6.299685375999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.129440322701606</v>
+        <v>0.1303444872668612</v>
       </c>
       <c r="T25">
-        <v>1.090113792378</v>
+        <v>1.10189808769547</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.118252898723733</v>
+        <v>2.029992361276911</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1132515703228145</v>
+        <v>0.1160045721653925</v>
       </c>
       <c r="C26">
-        <v>132.7768258247104</v>
+        <v>124.5886798405705</v>
       </c>
       <c r="D26">
-        <v>164.8428258247104</v>
+        <v>158.3786798405705</v>
       </c>
       <c r="E26">
-        <v>7.775999999999996</v>
+        <v>9.5</v>
       </c>
       <c r="F26">
-        <v>41.376</v>
+        <v>43.1</v>
       </c>
       <c r="G26">
         <v>9.31</v>
@@ -3413,45 +3413,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M26">
-        <v>3.1363008</v>
+        <v>3.879</v>
       </c>
       <c r="N26">
-        <v>3.230365866666666</v>
+        <v>2.487666666666666</v>
       </c>
       <c r="O26">
-        <v>0.7106804906666666</v>
+        <v>0.5472866666666666</v>
       </c>
       <c r="P26">
-        <v>2.519685376</v>
+        <v>1.94038</v>
       </c>
       <c r="Q26">
-        <v>6.299685376</v>
+        <v>5.72038</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1303444872668612</v>
+        <v>0.1312727628871899</v>
       </c>
       <c r="T26">
-        <v>1.10189808769547</v>
+        <v>1.113996630888072</v>
       </c>
       <c r="U26">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.029992361276912</v>
+        <v>1.641316490504425</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1160045721653925</v>
+        <v>0.1160993340079704</v>
       </c>
       <c r="C27">
-        <v>124.5886798405705</v>
+        <v>122.6511891192352</v>
       </c>
       <c r="D27">
-        <v>158.3786798405705</v>
+        <v>158.1651891192352</v>
       </c>
       <c r="E27">
-        <v>9.5</v>
+        <v>11.224</v>
       </c>
       <c r="F27">
-        <v>43.1</v>
+        <v>44.82400000000001</v>
       </c>
       <c r="G27">
         <v>9.31</v>
@@ -3495,28 +3495,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M27">
-        <v>3.879</v>
+        <v>4.03416</v>
       </c>
       <c r="N27">
-        <v>2.487666666666666</v>
+        <v>2.332506666666666</v>
       </c>
       <c r="O27">
-        <v>0.5472866666666666</v>
+        <v>0.5131514666666666</v>
       </c>
       <c r="P27">
-        <v>1.94038</v>
+        <v>1.8193552</v>
       </c>
       <c r="Q27">
-        <v>5.72038</v>
+        <v>5.5993552</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1312727628871899</v>
+        <v>0.1322261270377978</v>
       </c>
       <c r="T27">
-        <v>1.113996630888072</v>
+        <v>1.126422161734529</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.641316490504425</v>
+        <v>1.578188933177332</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1160993340079704</v>
+        <v>0.1161940958505483</v>
       </c>
       <c r="C28">
-        <v>122.6511891192352</v>
+        <v>120.7142731840062</v>
       </c>
       <c r="D28">
-        <v>158.1651891192352</v>
+        <v>157.9522731840062</v>
       </c>
       <c r="E28">
-        <v>11.224</v>
+        <v>12.948</v>
       </c>
       <c r="F28">
-        <v>44.82400000000001</v>
+        <v>46.548</v>
       </c>
       <c r="G28">
         <v>9.31</v>
@@ -3577,28 +3577,28 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M28">
-        <v>4.03416</v>
+        <v>4.18932</v>
       </c>
       <c r="N28">
-        <v>2.332506666666666</v>
+        <v>2.177346666666666</v>
       </c>
       <c r="O28">
-        <v>0.5131514666666666</v>
+        <v>0.4790162666666665</v>
       </c>
       <c r="P28">
-        <v>1.8193552</v>
+        <v>1.698330399999999</v>
       </c>
       <c r="Q28">
-        <v>5.5993552</v>
+        <v>5.4783304</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1322261270377978</v>
+        <v>0.1332056107541758</v>
       </c>
       <c r="T28">
-        <v>1.126422161734529</v>
+        <v>1.139188118083628</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.578188933177332</v>
+        <v>1.519737491207801</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1161940958505483</v>
+        <v>0.130036712063029</v>
       </c>
       <c r="C29">
-        <v>120.7142731840062</v>
+        <v>93.03398115851614</v>
       </c>
       <c r="D29">
-        <v>157.9522731840062</v>
+        <v>131.9959811585161</v>
       </c>
       <c r="E29">
-        <v>12.948</v>
+        <v>14.672</v>
       </c>
       <c r="F29">
-        <v>46.548</v>
+        <v>48.27200000000001</v>
       </c>
       <c r="G29">
         <v>9.31</v>
@@ -3659,45 +3659,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M29">
-        <v>4.18932</v>
+        <v>7.086329600000002</v>
       </c>
       <c r="N29">
-        <v>2.177346666666666</v>
+        <v>-0.7196629333333355</v>
       </c>
       <c r="O29">
-        <v>0.4790162666666665</v>
+        <v>-0.1583258453333338</v>
       </c>
       <c r="P29">
-        <v>1.698330399999999</v>
+        <v>-0.5613370880000017</v>
       </c>
       <c r="Q29">
-        <v>5.4783304</v>
+        <v>3.218662911999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1332056107541758</v>
+        <v>0.1348017065153137</v>
       </c>
       <c r="T29">
-        <v>1.139188118083628</v>
+        <v>1.159990596445409</v>
       </c>
       <c r="U29">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.22</v>
+        <v>0.197657566854732</v>
       </c>
       <c r="W29">
-        <v>0.0702</v>
+        <v>0.1177838691857254</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.519737491207801</v>
+        <v>0.8984434857033272</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.130036712063029</v>
+        <v>0.131046712063029</v>
       </c>
       <c r="C30">
-        <v>93.03398115851614</v>
+        <v>89.74609748788808</v>
       </c>
       <c r="D30">
-        <v>131.9959811585161</v>
+        <v>130.4320974878881</v>
       </c>
       <c r="E30">
-        <v>14.672</v>
+        <v>16.39600000000001</v>
       </c>
       <c r="F30">
-        <v>48.27200000000001</v>
+        <v>49.99600000000001</v>
       </c>
       <c r="G30">
         <v>9.31</v>
@@ -3741,37 +3741,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M30">
-        <v>7.086329600000002</v>
+        <v>7.339412800000002</v>
       </c>
       <c r="N30">
-        <v>-0.7196629333333355</v>
+        <v>-0.9727461333333354</v>
       </c>
       <c r="O30">
-        <v>-0.1583258453333338</v>
+        <v>-0.2140041493333338</v>
       </c>
       <c r="P30">
-        <v>-0.5613370880000017</v>
+        <v>-0.7587419840000016</v>
       </c>
       <c r="Q30">
-        <v>3.218662911999998</v>
+        <v>3.021258015999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1348017065153137</v>
+        <v>0.1360552516775012</v>
       </c>
       <c r="T30">
-        <v>1.159990596445409</v>
+        <v>1.176328492169992</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.197657566854732</v>
+        <v>0.1908417886873275</v>
       </c>
       <c r="W30">
-        <v>0.1177838691857254</v>
+        <v>0.1187844254207003</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8984434857033272</v>
+        <v>0.8674626758514884</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.131046712063029</v>
+        <v>0.132056712063029</v>
       </c>
       <c r="C31">
-        <v>89.74609748788809</v>
+        <v>86.49483757602752</v>
       </c>
       <c r="D31">
-        <v>130.4320974878881</v>
+        <v>128.9048375760275</v>
       </c>
       <c r="E31">
-        <v>16.39599999999999</v>
+        <v>18.12</v>
       </c>
       <c r="F31">
-        <v>49.996</v>
+        <v>51.72</v>
       </c>
       <c r="G31">
         <v>9.31</v>
@@ -3823,37 +3823,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M31">
-        <v>7.3394128</v>
+        <v>7.592496000000001</v>
       </c>
       <c r="N31">
-        <v>-0.9727461333333336</v>
+        <v>-1.225829333333334</v>
       </c>
       <c r="O31">
-        <v>-0.2140041493333334</v>
+        <v>-0.2696824533333336</v>
       </c>
       <c r="P31">
-        <v>-0.7587419840000003</v>
+        <v>-0.9561468800000008</v>
       </c>
       <c r="Q31">
-        <v>3.021258016</v>
+        <v>2.823853119999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1360552516775012</v>
+        <v>0.1373446124157512</v>
       </c>
       <c r="T31">
-        <v>1.176328492169992</v>
+        <v>1.193133184915278</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1908417886873275</v>
+        <v>0.1844803957310832</v>
       </c>
       <c r="W31">
-        <v>0.1187844254207003</v>
+        <v>0.119718277906677</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8674626758514886</v>
+        <v>0.8385472533231055</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.132056712063029</v>
+        <v>0.1330667120630289</v>
       </c>
       <c r="C32">
-        <v>86.49483757602752</v>
+        <v>83.27892980416426</v>
       </c>
       <c r="D32">
-        <v>128.9048375760275</v>
+        <v>127.4129298041643</v>
       </c>
       <c r="E32">
-        <v>18.12</v>
+        <v>19.844</v>
       </c>
       <c r="F32">
-        <v>51.72</v>
+        <v>53.444</v>
       </c>
       <c r="G32">
         <v>9.31</v>
@@ -3905,37 +3905,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M32">
-        <v>7.592496000000001</v>
+        <v>7.845579200000001</v>
       </c>
       <c r="N32">
-        <v>-1.225829333333334</v>
+        <v>-1.478912533333335</v>
       </c>
       <c r="O32">
-        <v>-0.2696824533333336</v>
+        <v>-0.3253607573333337</v>
       </c>
       <c r="P32">
-        <v>-0.9561468800000008</v>
+        <v>-1.153551776000001</v>
       </c>
       <c r="Q32">
-        <v>2.823853119999999</v>
+        <v>2.626448223999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1373446124157512</v>
+        <v>0.138671345929023</v>
       </c>
       <c r="T32">
-        <v>1.193133184915278</v>
+        <v>1.210424970203905</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1844803957310832</v>
+        <v>0.1785294152236289</v>
       </c>
       <c r="W32">
-        <v>0.119718277906677</v>
+        <v>0.1205918818451713</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8385472533231055</v>
+        <v>0.811497341925586</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1330667120630289</v>
+        <v>0.1523663338764533</v>
       </c>
       <c r="C33">
-        <v>83.27892980416426</v>
+        <v>58.47989972748361</v>
       </c>
       <c r="D33">
-        <v>127.4129298041643</v>
+        <v>104.3378997274836</v>
       </c>
       <c r="E33">
-        <v>19.844</v>
+        <v>21.568</v>
       </c>
       <c r="F33">
-        <v>53.444</v>
+        <v>55.16800000000001</v>
       </c>
       <c r="G33">
         <v>9.31</v>
@@ -3987,45 +3987,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M33">
-        <v>7.845579200000001</v>
+        <v>11.0777344</v>
       </c>
       <c r="N33">
-        <v>-1.478912533333335</v>
+        <v>-4.711067733333336</v>
       </c>
       <c r="O33">
-        <v>-0.3253607573333337</v>
+        <v>-1.036434901333334</v>
       </c>
       <c r="P33">
-        <v>-1.153551776000001</v>
+        <v>-3.674632832000002</v>
       </c>
       <c r="Q33">
-        <v>2.626448223999999</v>
+        <v>0.1053671679999981</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.138671345929023</v>
+        <v>0.1415218389771326</v>
       </c>
       <c r="T33">
-        <v>1.210424970203905</v>
+        <v>1.247576450332786</v>
       </c>
       <c r="U33">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1785294152236289</v>
+        <v>0.1264398130602108</v>
       </c>
       <c r="W33">
-        <v>0.1205918818451713</v>
+        <v>0.1754108855375097</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.811497341925586</v>
+        <v>0.5747264230009581</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1523663338764533</v>
+        <v>0.1539163338764533</v>
       </c>
       <c r="C34">
-        <v>58.47989972748361</v>
+        <v>55.26006890545069</v>
       </c>
       <c r="D34">
-        <v>104.3378997274836</v>
+        <v>102.8420689054507</v>
       </c>
       <c r="E34">
-        <v>21.568</v>
+        <v>23.292</v>
       </c>
       <c r="F34">
-        <v>55.16800000000001</v>
+        <v>56.892</v>
       </c>
       <c r="G34">
         <v>9.31</v>
@@ -4069,37 +4069,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M34">
-        <v>11.0777344</v>
+        <v>11.4239136</v>
       </c>
       <c r="N34">
-        <v>-4.711067733333336</v>
+        <v>-5.057246933333334</v>
       </c>
       <c r="O34">
-        <v>-1.036434901333334</v>
+        <v>-1.112594325333333</v>
       </c>
       <c r="P34">
-        <v>-3.674632832000002</v>
+        <v>-3.944652608000001</v>
       </c>
       <c r="Q34">
-        <v>0.1053671679999981</v>
+        <v>-0.1646526080000008</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1415218389771326</v>
+        <v>0.1429505231409704</v>
       </c>
       <c r="T34">
-        <v>1.247576450332786</v>
+        <v>1.266196994367603</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1264398130602108</v>
+        <v>0.1226083035735377</v>
       </c>
       <c r="W34">
-        <v>0.1754108855375097</v>
+        <v>0.1761802526424336</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5747264230009581</v>
+        <v>0.5573104707888079</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1539163338764533</v>
+        <v>0.1554663338764533</v>
       </c>
       <c r="C35">
-        <v>55.26006890545069</v>
+        <v>52.08252157539194</v>
       </c>
       <c r="D35">
-        <v>102.8420689054507</v>
+        <v>101.3885215753919</v>
       </c>
       <c r="E35">
-        <v>23.292</v>
+        <v>25.01600000000001</v>
       </c>
       <c r="F35">
-        <v>56.892</v>
+        <v>58.61600000000001</v>
       </c>
       <c r="G35">
         <v>9.31</v>
@@ -4151,37 +4151,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M35">
-        <v>11.4239136</v>
+        <v>11.7700928</v>
       </c>
       <c r="N35">
-        <v>-5.057246933333334</v>
+        <v>-5.403426133333336</v>
       </c>
       <c r="O35">
-        <v>-1.112594325333333</v>
+        <v>-1.188753749333334</v>
       </c>
       <c r="P35">
-        <v>-3.944652608000001</v>
+        <v>-4.214672384000002</v>
       </c>
       <c r="Q35">
-        <v>-0.1646526080000008</v>
+        <v>-0.4346723840000015</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1429505231409704</v>
+        <v>0.1444225007643185</v>
       </c>
       <c r="T35">
-        <v>1.266196994367603</v>
+        <v>1.285381797312567</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1226083035735377</v>
+        <v>0.1190021769978454</v>
       </c>
       <c r="W35">
-        <v>0.1761802526424336</v>
+        <v>0.1769043628588327</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5573104707888079</v>
+        <v>0.5409189863538429</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1554663338764533</v>
+        <v>0.1570163338764533</v>
       </c>
       <c r="C36">
-        <v>52.08252157539194</v>
+        <v>48.94548984736867</v>
       </c>
       <c r="D36">
-        <v>101.3885215753919</v>
+        <v>99.97548984736868</v>
       </c>
       <c r="E36">
-        <v>25.01600000000001</v>
+        <v>26.74000000000001</v>
       </c>
       <c r="F36">
-        <v>58.61600000000001</v>
+        <v>60.34000000000001</v>
       </c>
       <c r="G36">
         <v>9.31</v>
@@ -4233,37 +4233,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M36">
-        <v>11.7700928</v>
+        <v>12.116272</v>
       </c>
       <c r="N36">
-        <v>-5.403426133333336</v>
+        <v>-5.749605333333336</v>
       </c>
       <c r="O36">
-        <v>-1.188753749333334</v>
+        <v>-1.264913173333334</v>
       </c>
       <c r="P36">
-        <v>-4.214672384000002</v>
+        <v>-4.484692160000002</v>
       </c>
       <c r="Q36">
-        <v>-0.4346723840000015</v>
+        <v>-0.7046921600000013</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1444225007643185</v>
+        <v>0.1459397700068464</v>
       </c>
       <c r="T36">
-        <v>1.285381797312567</v>
+        <v>1.305156901886606</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1190021769978454</v>
+        <v>0.115602114797907</v>
       </c>
       <c r="W36">
-        <v>0.1769043628588327</v>
+        <v>0.1775870953485803</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5409189863538429</v>
+        <v>0.5254641581723045</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1570163338764533</v>
+        <v>0.1585663338764533</v>
       </c>
       <c r="C37">
-        <v>48.94548984736867</v>
+        <v>45.84730303170792</v>
       </c>
       <c r="D37">
-        <v>99.97548984736868</v>
+        <v>98.60130303170793</v>
       </c>
       <c r="E37">
-        <v>26.74000000000001</v>
+        <v>28.46400000000001</v>
       </c>
       <c r="F37">
-        <v>60.34000000000001</v>
+        <v>62.06400000000001</v>
       </c>
       <c r="G37">
         <v>9.31</v>
@@ -4315,37 +4315,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M37">
-        <v>12.116272</v>
+        <v>12.4624512</v>
       </c>
       <c r="N37">
-        <v>-5.749605333333336</v>
+        <v>-6.095784533333336</v>
       </c>
       <c r="O37">
-        <v>-1.264913173333334</v>
+        <v>-1.341072597333334</v>
       </c>
       <c r="P37">
-        <v>-4.484692160000002</v>
+        <v>-4.754711936000001</v>
       </c>
       <c r="Q37">
-        <v>-0.7046921600000013</v>
+        <v>-0.9747119360000012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1459397700068464</v>
+        <v>0.1475044539132034</v>
       </c>
       <c r="T37">
-        <v>1.305156901886606</v>
+        <v>1.325549978478585</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.115602114797907</v>
+        <v>0.1123909449424096</v>
       </c>
       <c r="W37">
-        <v>0.1775870953485803</v>
+        <v>0.1782318982555642</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5254641581723045</v>
+        <v>0.5108679315564073</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1585663338764533</v>
+        <v>0.1734737284730491</v>
       </c>
       <c r="C38">
-        <v>45.84730303170793</v>
+        <v>32.61045266216245</v>
       </c>
       <c r="D38">
-        <v>98.60130303170793</v>
+        <v>87.08845266216245</v>
       </c>
       <c r="E38">
-        <v>28.464</v>
+        <v>30.188</v>
       </c>
       <c r="F38">
-        <v>62.064</v>
+        <v>63.788</v>
       </c>
       <c r="G38">
         <v>9.31</v>
@@ -4397,45 +4397,45 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M38">
-        <v>12.4624512</v>
+        <v>15.0412104</v>
       </c>
       <c r="N38">
-        <v>-6.095784533333334</v>
+        <v>-8.674543733333334</v>
       </c>
       <c r="O38">
-        <v>-1.341072597333334</v>
+        <v>-1.908399621333333</v>
       </c>
       <c r="P38">
-        <v>-4.754711936000001</v>
+        <v>-6.766144112</v>
       </c>
       <c r="Q38">
-        <v>-0.9747119360000003</v>
+        <v>-2.986144112</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1475044539132034</v>
+        <v>0.1497654684143588</v>
       </c>
       <c r="T38">
-        <v>1.325549978478585</v>
+        <v>1.355018577030857</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1123909449424096</v>
+        <v>0.09312193828939901</v>
       </c>
       <c r="W38">
-        <v>0.1782318982555642</v>
+        <v>0.2138418469513597</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5108679315564073</v>
+        <v>0.4232815376790865</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1734737284730491</v>
+        <v>0.1753737284730491</v>
       </c>
       <c r="C39">
-        <v>32.61045266216245</v>
+        <v>29.6094340719895</v>
       </c>
       <c r="D39">
-        <v>87.08845266216245</v>
+        <v>85.8114340719895</v>
       </c>
       <c r="E39">
-        <v>30.188</v>
+        <v>31.912</v>
       </c>
       <c r="F39">
-        <v>63.788</v>
+        <v>65.512</v>
       </c>
       <c r="G39">
         <v>9.31</v>
@@ -4479,37 +4479,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M39">
-        <v>15.0412104</v>
+        <v>15.4477296</v>
       </c>
       <c r="N39">
-        <v>-8.674543733333334</v>
+        <v>-9.081062933333335</v>
       </c>
       <c r="O39">
-        <v>-1.908399621333333</v>
+        <v>-1.997833845333334</v>
       </c>
       <c r="P39">
-        <v>-6.766144112</v>
+        <v>-7.083229088000001</v>
       </c>
       <c r="Q39">
-        <v>-2.986144112</v>
+        <v>-3.303229088000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1497654684143588</v>
+        <v>0.1514423308081387</v>
       </c>
       <c r="T39">
-        <v>1.355018577030857</v>
+        <v>1.376873715370064</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09312193828939901</v>
+        <v>0.09067136096599376</v>
       </c>
       <c r="W39">
-        <v>0.2138418469513597</v>
+        <v>0.2144196930842187</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4232815376790865</v>
+        <v>0.4121425498454262</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1753737284730491</v>
+        <v>0.1772737284730491</v>
       </c>
       <c r="C40">
-        <v>29.6094340719895</v>
+        <v>26.64532529413428</v>
       </c>
       <c r="D40">
-        <v>85.8114340719895</v>
+        <v>84.57132529413428</v>
       </c>
       <c r="E40">
-        <v>31.912</v>
+        <v>33.636</v>
       </c>
       <c r="F40">
-        <v>65.512</v>
+        <v>67.236</v>
       </c>
       <c r="G40">
         <v>9.31</v>
@@ -4561,37 +4561,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M40">
-        <v>15.4477296</v>
+        <v>15.8542488</v>
       </c>
       <c r="N40">
-        <v>-9.081062933333335</v>
+        <v>-9.487582133333337</v>
       </c>
       <c r="O40">
-        <v>-1.997833845333334</v>
+        <v>-2.087268069333334</v>
       </c>
       <c r="P40">
-        <v>-7.083229088000001</v>
+        <v>-7.400314064000003</v>
       </c>
       <c r="Q40">
-        <v>-3.303229088000001</v>
+        <v>-3.620314064000003</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1514423308081387</v>
+        <v>0.1531741722967968</v>
       </c>
       <c r="T40">
-        <v>1.376873715370064</v>
+        <v>1.399445415622032</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09067136096599376</v>
+        <v>0.08834645427455802</v>
       </c>
       <c r="W40">
-        <v>0.2144196930842187</v>
+        <v>0.2149679060820592</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4121425498454262</v>
+        <v>0.4015747921570818</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1772737284730491</v>
+        <v>0.1791737284730491</v>
       </c>
       <c r="C41">
-        <v>26.64532529413428</v>
+        <v>23.71654891201996</v>
       </c>
       <c r="D41">
-        <v>84.57132529413428</v>
+        <v>83.36654891201997</v>
       </c>
       <c r="E41">
-        <v>33.636</v>
+        <v>35.36000000000001</v>
       </c>
       <c r="F41">
-        <v>67.236</v>
+        <v>68.96000000000001</v>
       </c>
       <c r="G41">
         <v>9.31</v>
@@ -4643,37 +4643,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M41">
-        <v>15.8542488</v>
+        <v>16.260768</v>
       </c>
       <c r="N41">
-        <v>-9.487582133333337</v>
+        <v>-9.894101333333335</v>
       </c>
       <c r="O41">
-        <v>-2.087268069333334</v>
+        <v>-2.176702293333334</v>
       </c>
       <c r="P41">
-        <v>-7.400314064000003</v>
+        <v>-7.717399040000002</v>
       </c>
       <c r="Q41">
-        <v>-3.620314064000003</v>
+        <v>-3.937399040000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1531741722967968</v>
+        <v>0.1549637418350767</v>
       </c>
       <c r="T41">
-        <v>1.399445415622032</v>
+        <v>1.422769505882399</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08834645427455802</v>
+        <v>0.08613779291769406</v>
       </c>
       <c r="W41">
-        <v>0.2149679060820592</v>
+        <v>0.2154887084300078</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4015747921570818</v>
+        <v>0.391535422353155</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1791737284730491</v>
+        <v>0.1810737284730491</v>
       </c>
       <c r="C42">
-        <v>23.71654891201996</v>
+        <v>20.82161613208704</v>
       </c>
       <c r="D42">
-        <v>83.36654891201997</v>
+        <v>82.19561613208705</v>
       </c>
       <c r="E42">
-        <v>35.36000000000001</v>
+        <v>37.08400000000001</v>
       </c>
       <c r="F42">
-        <v>68.96000000000001</v>
+        <v>70.68400000000001</v>
       </c>
       <c r="G42">
         <v>9.31</v>
@@ -4725,37 +4725,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M42">
-        <v>16.260768</v>
+        <v>16.6672872</v>
       </c>
       <c r="N42">
-        <v>-9.894101333333335</v>
+        <v>-10.30062053333334</v>
       </c>
       <c r="O42">
-        <v>-2.176702293333334</v>
+        <v>-2.266136517333334</v>
       </c>
       <c r="P42">
-        <v>-7.717399040000002</v>
+        <v>-8.034484016000002</v>
       </c>
       <c r="Q42">
-        <v>-3.937399040000002</v>
+        <v>-4.254484016000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1549637418350767</v>
+        <v>0.1568139747475356</v>
       </c>
       <c r="T42">
-        <v>1.422769505882399</v>
+        <v>1.446884243270237</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08613779291769406</v>
+        <v>0.08403687113921372</v>
       </c>
       <c r="W42">
-        <v>0.2154887084300078</v>
+        <v>0.2159841057853734</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.391535422353155</v>
+        <v>0.3819857779055169</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1810737284730491</v>
+        <v>0.1829737284730491</v>
       </c>
       <c r="C43">
-        <v>20.82161613208704</v>
+        <v>17.95912064618467</v>
       </c>
       <c r="D43">
-        <v>82.19561613208705</v>
+        <v>81.05712064618469</v>
       </c>
       <c r="E43">
-        <v>37.08400000000001</v>
+        <v>38.80800000000001</v>
       </c>
       <c r="F43">
-        <v>70.68400000000001</v>
+        <v>72.40800000000002</v>
       </c>
       <c r="G43">
         <v>9.31</v>
@@ -4807,37 +4807,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M43">
-        <v>16.6672872</v>
+        <v>17.07380640000001</v>
       </c>
       <c r="N43">
-        <v>-10.30062053333334</v>
+        <v>-10.70713973333334</v>
       </c>
       <c r="O43">
-        <v>-2.266136517333334</v>
+        <v>-2.355570741333334</v>
       </c>
       <c r="P43">
-        <v>-8.034484016000002</v>
+        <v>-8.351568992000004</v>
       </c>
       <c r="Q43">
-        <v>-4.254484016000002</v>
+        <v>-4.571568992000004</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1568139747475356</v>
+        <v>0.1587280087949069</v>
       </c>
       <c r="T43">
-        <v>1.446884243270237</v>
+        <v>1.47183052332662</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08403687113921372</v>
+        <v>0.08203599325494672</v>
       </c>
       <c r="W43">
-        <v>0.2159841057853734</v>
+        <v>0.2164559127904836</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3819857779055169</v>
+        <v>0.3728908784315761</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1829737284730491</v>
+        <v>0.1848737284730491</v>
       </c>
       <c r="C44">
-        <v>17.95912064618469</v>
+        <v>15.12773299706737</v>
       </c>
       <c r="D44">
-        <v>81.05712064618469</v>
+        <v>79.94973299706737</v>
       </c>
       <c r="E44">
-        <v>38.808</v>
+        <v>40.532</v>
       </c>
       <c r="F44">
-        <v>72.408</v>
+        <v>74.13200000000001</v>
       </c>
       <c r="G44">
         <v>9.31</v>
@@ -4889,37 +4889,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M44">
-        <v>17.0738064</v>
+        <v>17.4803256</v>
       </c>
       <c r="N44">
-        <v>-10.70713973333334</v>
+        <v>-11.11365893333333</v>
       </c>
       <c r="O44">
-        <v>-2.355570741333334</v>
+        <v>-2.445004965333333</v>
       </c>
       <c r="P44">
-        <v>-8.351568992000001</v>
+        <v>-8.668653968000001</v>
       </c>
       <c r="Q44">
-        <v>-4.571568992</v>
+        <v>-4.888653968000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1587280087949069</v>
+        <v>0.1607092019316597</v>
       </c>
       <c r="T44">
-        <v>1.47183052332662</v>
+        <v>1.497652111455157</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08203599325494675</v>
+        <v>0.08012817945832007</v>
       </c>
       <c r="W44">
-        <v>0.2164559127904836</v>
+        <v>0.2169057752837281</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3728908784315761</v>
+        <v>0.3642189975378186</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1848737284730491</v>
+        <v>0.1867737284730491</v>
       </c>
       <c r="C45">
-        <v>15.12773299706737</v>
+        <v>12.32619539953215</v>
       </c>
       <c r="D45">
-        <v>79.94973299706737</v>
+        <v>78.87219539953216</v>
       </c>
       <c r="E45">
-        <v>40.532</v>
+        <v>42.25600000000001</v>
       </c>
       <c r="F45">
-        <v>74.13200000000001</v>
+        <v>75.85600000000001</v>
       </c>
       <c r="G45">
         <v>9.31</v>
@@ -4971,37 +4971,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M45">
-        <v>17.4803256</v>
+        <v>17.8868448</v>
       </c>
       <c r="N45">
-        <v>-11.11365893333333</v>
+        <v>-11.52017813333334</v>
       </c>
       <c r="O45">
-        <v>-2.445004965333333</v>
+        <v>-2.534439189333334</v>
       </c>
       <c r="P45">
-        <v>-8.668653968000001</v>
+        <v>-8.985738944000001</v>
       </c>
       <c r="Q45">
-        <v>-4.888653968000001</v>
+        <v>-5.205738944000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1607092019316597</v>
+        <v>0.1627611519661536</v>
       </c>
       <c r="T45">
-        <v>1.497652111455157</v>
+        <v>1.524395899159714</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08012817945832007</v>
+        <v>0.07830708447063098</v>
       </c>
       <c r="W45">
-        <v>0.2169057752837281</v>
+        <v>0.2173351894818252</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3642189975378186</v>
+        <v>0.3559412930483227</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1867737284730491</v>
+        <v>0.1886737284730491</v>
       </c>
       <c r="C46">
-        <v>12.32619539953215</v>
+        <v>9.553316974781183</v>
       </c>
       <c r="D46">
-        <v>78.87219539953216</v>
+        <v>77.82331697478118</v>
       </c>
       <c r="E46">
-        <v>42.25600000000001</v>
+        <v>43.98</v>
       </c>
       <c r="F46">
-        <v>75.85600000000001</v>
+        <v>77.58</v>
       </c>
       <c r="G46">
         <v>9.31</v>
@@ -5053,37 +5053,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M46">
-        <v>17.8868448</v>
+        <v>18.293364</v>
       </c>
       <c r="N46">
-        <v>-11.52017813333334</v>
+        <v>-11.92669733333333</v>
       </c>
       <c r="O46">
-        <v>-2.534439189333334</v>
+        <v>-2.623873413333333</v>
       </c>
       <c r="P46">
-        <v>-8.985738944000001</v>
+        <v>-9.30282392</v>
       </c>
       <c r="Q46">
-        <v>-5.205738944000001</v>
+        <v>-5.52282392</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1627611519661536</v>
+        <v>0.1648877183655382</v>
       </c>
       <c r="T46">
-        <v>1.524395899159714</v>
+        <v>1.552112188235345</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07830708447063098</v>
+        <v>0.07656692703795029</v>
       </c>
       <c r="W46">
-        <v>0.2173351894818252</v>
+        <v>0.2177455186044513</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3559412930483227</v>
+        <v>0.3480314865361378</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1886737284730491</v>
+        <v>0.1905737284730491</v>
       </c>
       <c r="C47">
-        <v>9.553316974781183</v>
+        <v>6.807969360047267</v>
       </c>
       <c r="D47">
-        <v>77.82331697478118</v>
+        <v>76.80196936004727</v>
       </c>
       <c r="E47">
-        <v>43.98</v>
+        <v>45.704</v>
       </c>
       <c r="F47">
-        <v>77.58</v>
+        <v>79.304</v>
       </c>
       <c r="G47">
         <v>9.31</v>
@@ -5135,37 +5135,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M47">
-        <v>18.293364</v>
+        <v>18.6998832</v>
       </c>
       <c r="N47">
-        <v>-11.92669733333333</v>
+        <v>-12.33321653333334</v>
       </c>
       <c r="O47">
-        <v>-2.623873413333333</v>
+        <v>-2.713307637333334</v>
       </c>
       <c r="P47">
-        <v>-9.30282392</v>
+        <v>-9.619908896000002</v>
       </c>
       <c r="Q47">
-        <v>-5.52282392</v>
+        <v>-5.839908896000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1648877183655382</v>
+        <v>0.1670930464834186</v>
       </c>
       <c r="T47">
-        <v>1.552112188235345</v>
+        <v>1.580855006535999</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07656692703795029</v>
+        <v>0.07490242862408181</v>
       </c>
       <c r="W47">
-        <v>0.2177455186044513</v>
+        <v>0.2181380073304415</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3480314865361378</v>
+        <v>0.3404655846549174</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1905737284730491</v>
+        <v>0.1924737284730491</v>
       </c>
       <c r="C48">
-        <v>6.807969360047267</v>
+        <v>4.089082659455173</v>
       </c>
       <c r="D48">
-        <v>76.80196936004727</v>
+        <v>75.80708265945518</v>
       </c>
       <c r="E48">
-        <v>45.704</v>
+        <v>47.428</v>
       </c>
       <c r="F48">
-        <v>79.304</v>
+        <v>81.02800000000001</v>
       </c>
       <c r="G48">
         <v>9.31</v>
@@ -5217,37 +5217,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M48">
-        <v>18.6998832</v>
+        <v>19.1064024</v>
       </c>
       <c r="N48">
-        <v>-12.33321653333334</v>
+        <v>-12.73973573333334</v>
       </c>
       <c r="O48">
-        <v>-2.713307637333334</v>
+        <v>-2.802741861333334</v>
       </c>
       <c r="P48">
-        <v>-9.619908896000002</v>
+        <v>-9.936993872000002</v>
       </c>
       <c r="Q48">
-        <v>-5.839908896000002</v>
+        <v>-6.156993872000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1670930464834186</v>
+        <v>0.1693815945302755</v>
       </c>
       <c r="T48">
-        <v>1.580855006535999</v>
+        <v>1.610682459489509</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07490242862408181</v>
+        <v>0.07330875992995241</v>
       </c>
       <c r="W48">
-        <v>0.2181380073304415</v>
+        <v>0.2185137944085172</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3404655846549174</v>
+        <v>0.3332216360452382</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1924737284730491</v>
+        <v>0.1943737284730491</v>
       </c>
       <c r="C49">
-        <v>4.089082659455173</v>
+        <v>1.395641705571521</v>
       </c>
       <c r="D49">
-        <v>75.80708265945518</v>
+        <v>74.83764170557153</v>
       </c>
       <c r="E49">
-        <v>47.428</v>
+        <v>49.15200000000001</v>
       </c>
       <c r="F49">
-        <v>81.02800000000001</v>
+        <v>82.75200000000001</v>
       </c>
       <c r="G49">
         <v>9.31</v>
@@ -5299,37 +5299,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M49">
-        <v>19.1064024</v>
+        <v>19.5129216</v>
       </c>
       <c r="N49">
-        <v>-12.73973573333334</v>
+        <v>-13.14625493333333</v>
       </c>
       <c r="O49">
-        <v>-2.802741861333334</v>
+        <v>-2.892176085333334</v>
       </c>
       <c r="P49">
-        <v>-9.936993872000002</v>
+        <v>-10.254078848</v>
       </c>
       <c r="Q49">
-        <v>-6.156993872000002</v>
+        <v>-6.474078848</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1693815945302755</v>
+        <v>0.1717581636558577</v>
       </c>
       <c r="T49">
-        <v>1.610682459489509</v>
+        <v>1.641657122172</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07330875992995241</v>
+        <v>0.07178149409807839</v>
       </c>
       <c r="W49">
-        <v>0.2185137944085172</v>
+        <v>0.2188739236916731</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3332216360452382</v>
+        <v>0.3262795186276292</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1943737284730491</v>
+        <v>0.1962737284730491</v>
       </c>
       <c r="C50">
-        <v>1.395641705571535</v>
+        <v>-1.273317395817756</v>
       </c>
       <c r="D50">
-        <v>74.83764170557153</v>
+        <v>73.89268260418224</v>
       </c>
       <c r="E50">
-        <v>49.15199999999999</v>
+        <v>50.876</v>
       </c>
       <c r="F50">
-        <v>82.752</v>
+        <v>84.476</v>
       </c>
       <c r="G50">
         <v>9.31</v>
@@ -5381,37 +5381,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M50">
-        <v>19.5129216</v>
+        <v>19.9194408</v>
       </c>
       <c r="N50">
-        <v>-13.14625493333333</v>
+        <v>-13.55277413333333</v>
       </c>
       <c r="O50">
-        <v>-2.892176085333333</v>
+        <v>-2.981610309333333</v>
       </c>
       <c r="P50">
-        <v>-10.254078848</v>
+        <v>-10.571163824</v>
       </c>
       <c r="Q50">
-        <v>-6.474078847999999</v>
+        <v>-6.791163823999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1717581636558577</v>
+        <v>0.1742279315706785</v>
       </c>
       <c r="T50">
-        <v>1.641657122172</v>
+        <v>1.673846477508705</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07178149409807841</v>
+        <v>0.07031656564709721</v>
       </c>
       <c r="W50">
-        <v>0.2188739236916731</v>
+        <v>0.2192193538204145</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3262795186276292</v>
+        <v>0.3196207529413509</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1962737284730491</v>
+        <v>0.1981737284730491</v>
       </c>
       <c r="C51">
-        <v>-1.273317395817756</v>
+        <v>-3.918710462423562</v>
       </c>
       <c r="D51">
-        <v>73.89268260418224</v>
+        <v>72.97128953757644</v>
       </c>
       <c r="E51">
-        <v>50.876</v>
+        <v>52.6</v>
       </c>
       <c r="F51">
-        <v>84.476</v>
+        <v>86.2</v>
       </c>
       <c r="G51">
         <v>9.31</v>
@@ -5463,37 +5463,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M51">
-        <v>19.9194408</v>
+        <v>20.32596</v>
       </c>
       <c r="N51">
-        <v>-13.55277413333333</v>
+        <v>-13.95929333333333</v>
       </c>
       <c r="O51">
-        <v>-2.981610309333333</v>
+        <v>-3.071044533333334</v>
       </c>
       <c r="P51">
-        <v>-10.571163824</v>
+        <v>-10.8882488</v>
       </c>
       <c r="Q51">
-        <v>-6.791163823999999</v>
+        <v>-7.108248800000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1742279315706785</v>
+        <v>0.176796490202092</v>
       </c>
       <c r="T51">
-        <v>1.673846477508705</v>
+        <v>1.707323407058879</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07031656564709721</v>
+        <v>0.06891023433415526</v>
       </c>
       <c r="W51">
-        <v>0.2192193538204145</v>
+        <v>0.2195509667440062</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3196207529413509</v>
+        <v>0.3132283378825239</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1981737284730491</v>
+        <v>0.2000737284730491</v>
       </c>
       <c r="C52">
-        <v>-3.918710462423562</v>
+        <v>-6.54140819594997</v>
       </c>
       <c r="D52">
-        <v>72.97128953757644</v>
+        <v>72.07259180405003</v>
       </c>
       <c r="E52">
-        <v>52.6</v>
+        <v>54.32400000000001</v>
       </c>
       <c r="F52">
-        <v>86.2</v>
+        <v>87.92400000000001</v>
       </c>
       <c r="G52">
         <v>9.31</v>
@@ -5545,37 +5545,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M52">
-        <v>20.32596</v>
+        <v>20.7324792</v>
       </c>
       <c r="N52">
-        <v>-13.95929333333333</v>
+        <v>-14.36581253333334</v>
       </c>
       <c r="O52">
-        <v>-3.071044533333334</v>
+        <v>-3.160478757333334</v>
       </c>
       <c r="P52">
-        <v>-10.8882488</v>
+        <v>-11.205333776</v>
       </c>
       <c r="Q52">
-        <v>-7.108248800000001</v>
+        <v>-7.425333776000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.176796490202092</v>
+        <v>0.1794698879613184</v>
       </c>
       <c r="T52">
-        <v>1.707323407058879</v>
+        <v>1.742166741896816</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06891023433415526</v>
+        <v>0.06755905326877966</v>
       </c>
       <c r="W52">
-        <v>0.2195509667440062</v>
+        <v>0.2198695752392218</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3132283378825239</v>
+        <v>0.3070866057671803</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2000737284730491</v>
+        <v>0.2019737284730491</v>
       </c>
       <c r="C53">
-        <v>-6.54140819594997</v>
+        <v>-9.142238926486883</v>
       </c>
       <c r="D53">
-        <v>72.07259180405003</v>
+        <v>71.19576107351313</v>
       </c>
       <c r="E53">
-        <v>54.32400000000001</v>
+        <v>56.04800000000001</v>
       </c>
       <c r="F53">
-        <v>87.92400000000001</v>
+        <v>89.64800000000001</v>
       </c>
       <c r="G53">
         <v>9.31</v>
@@ -5627,37 +5627,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M53">
-        <v>20.7324792</v>
+        <v>21.1389984</v>
       </c>
       <c r="N53">
-        <v>-14.36581253333334</v>
+        <v>-14.77233173333333</v>
       </c>
       <c r="O53">
-        <v>-3.160478757333334</v>
+        <v>-3.249912981333334</v>
       </c>
       <c r="P53">
-        <v>-11.205333776</v>
+        <v>-11.522418752</v>
       </c>
       <c r="Q53">
-        <v>-7.425333776000003</v>
+        <v>-7.742418752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1794698879613184</v>
+        <v>0.1822546772938459</v>
       </c>
       <c r="T53">
-        <v>1.742166741896816</v>
+        <v>1.778461882353</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06755905326877966</v>
+        <v>0.06625984070591852</v>
       </c>
       <c r="W53">
-        <v>0.2198695752392218</v>
+        <v>0.2201759295615444</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3070866057671803</v>
+        <v>0.3011810941178115</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2019737284730491</v>
+        <v>0.2038737284730491</v>
       </c>
       <c r="C54">
-        <v>-9.142238926486883</v>
+        <v>-11.72199115898222</v>
       </c>
       <c r="D54">
-        <v>71.19576107351313</v>
+        <v>70.34000884101779</v>
       </c>
       <c r="E54">
-        <v>56.04800000000001</v>
+        <v>57.77200000000001</v>
       </c>
       <c r="F54">
-        <v>89.64800000000001</v>
+        <v>91.37200000000001</v>
       </c>
       <c r="G54">
         <v>9.31</v>
@@ -5709,37 +5709,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M54">
-        <v>21.1389984</v>
+        <v>21.5455176</v>
       </c>
       <c r="N54">
-        <v>-14.77233173333333</v>
+        <v>-15.17885093333334</v>
       </c>
       <c r="O54">
-        <v>-3.249912981333334</v>
+        <v>-3.339347205333334</v>
       </c>
       <c r="P54">
-        <v>-11.522418752</v>
+        <v>-11.839503728</v>
       </c>
       <c r="Q54">
-        <v>-7.742418752</v>
+        <v>-8.059503728000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1822546772938459</v>
+        <v>0.1851579683000979</v>
       </c>
       <c r="T54">
-        <v>1.778461882353</v>
+        <v>1.816301496871148</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06625984070591852</v>
+        <v>0.06500965503222193</v>
       </c>
       <c r="W54">
-        <v>0.2201759295615444</v>
+        <v>0.2204707233434021</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3011810941178115</v>
+        <v>0.2954984319646452</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2038737284730491</v>
+        <v>0.2057737284730491</v>
       </c>
       <c r="C55">
-        <v>-11.72199115898222</v>
+        <v>-14.28141593824807</v>
       </c>
       <c r="D55">
-        <v>70.34000884101779</v>
+        <v>69.50458406175193</v>
       </c>
       <c r="E55">
-        <v>57.77200000000001</v>
+        <v>59.496</v>
       </c>
       <c r="F55">
-        <v>91.37200000000001</v>
+        <v>93.096</v>
       </c>
       <c r="G55">
         <v>9.31</v>
@@ -5791,37 +5791,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M55">
-        <v>21.5455176</v>
+        <v>21.9520368</v>
       </c>
       <c r="N55">
-        <v>-15.17885093333334</v>
+        <v>-15.58537013333333</v>
       </c>
       <c r="O55">
-        <v>-3.339347205333334</v>
+        <v>-3.428781429333334</v>
       </c>
       <c r="P55">
-        <v>-11.839503728</v>
+        <v>-12.156588704</v>
       </c>
       <c r="Q55">
-        <v>-8.059503728000003</v>
+        <v>-8.376588704</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1851579683000979</v>
+        <v>0.1881874893501</v>
       </c>
       <c r="T55">
-        <v>1.816301496871148</v>
+        <v>1.855786312020521</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06500965503222193</v>
+        <v>0.06380577253162524</v>
       </c>
       <c r="W55">
-        <v>0.2204707233434021</v>
+        <v>0.2207545988370428</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2954984319646452</v>
+        <v>0.2900262387801148</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2057737284730491</v>
+        <v>0.2076737284730491</v>
       </c>
       <c r="C56">
-        <v>-14.28141593824807</v>
+        <v>-16.8212290474106</v>
       </c>
       <c r="D56">
-        <v>69.50458406175193</v>
+        <v>68.68877095258941</v>
       </c>
       <c r="E56">
-        <v>59.496</v>
+        <v>61.22000000000001</v>
       </c>
       <c r="F56">
-        <v>93.096</v>
+        <v>94.82000000000001</v>
       </c>
       <c r="G56">
         <v>9.31</v>
@@ -5873,37 +5873,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M56">
-        <v>21.9520368</v>
+        <v>22.358556</v>
       </c>
       <c r="N56">
-        <v>-15.58537013333333</v>
+        <v>-15.99188933333334</v>
       </c>
       <c r="O56">
-        <v>-3.428781429333334</v>
+        <v>-3.518215653333334</v>
       </c>
       <c r="P56">
-        <v>-12.156588704</v>
+        <v>-12.47367368</v>
       </c>
       <c r="Q56">
-        <v>-8.376588704</v>
+        <v>-8.693673680000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1881874893501</v>
+        <v>0.1913516557801023</v>
       </c>
       <c r="T56">
-        <v>1.855786312020521</v>
+        <v>1.8970260078432</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06380577253162524</v>
+        <v>0.06264566757650478</v>
       </c>
       <c r="W56">
-        <v>0.2207545988370428</v>
+        <v>0.2210281515854602</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2900262387801148</v>
+        <v>0.2847530344386581</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2076737284730491</v>
+        <v>0.2095737284730491</v>
       </c>
       <c r="C57">
-        <v>-16.8212290474106</v>
+        <v>-19.34211305332975</v>
       </c>
       <c r="D57">
-        <v>68.68877095258941</v>
+        <v>67.89188694667025</v>
       </c>
       <c r="E57">
-        <v>61.22000000000001</v>
+        <v>62.94400000000001</v>
       </c>
       <c r="F57">
-        <v>94.82000000000001</v>
+        <v>96.54400000000001</v>
       </c>
       <c r="G57">
         <v>9.31</v>
@@ -5955,37 +5955,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M57">
-        <v>22.358556</v>
+        <v>22.7650752</v>
       </c>
       <c r="N57">
-        <v>-15.99188933333334</v>
+        <v>-16.39840853333333</v>
       </c>
       <c r="O57">
-        <v>-3.518215653333334</v>
+        <v>-3.607649877333334</v>
       </c>
       <c r="P57">
-        <v>-12.47367368</v>
+        <v>-12.790758656</v>
       </c>
       <c r="Q57">
-        <v>-8.693673680000003</v>
+        <v>-9.010758656</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1913516557801023</v>
+        <v>0.1946596479569228</v>
       </c>
       <c r="T57">
-        <v>1.8970260078432</v>
+        <v>1.940140235294181</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06264566757650478</v>
+        <v>0.06152699494121006</v>
       </c>
       <c r="W57">
-        <v>0.2210281515854602</v>
+        <v>0.2212919345928627</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2847530344386581</v>
+        <v>0.2796681588236821</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2095737284730491</v>
+        <v>0.2114737284730491</v>
       </c>
       <c r="C58">
-        <v>-19.34211305332975</v>
+        <v>-21.84471921127385</v>
       </c>
       <c r="D58">
-        <v>67.89188694667025</v>
+        <v>67.11328078872616</v>
       </c>
       <c r="E58">
-        <v>62.94400000000001</v>
+        <v>64.66800000000001</v>
       </c>
       <c r="F58">
-        <v>96.54400000000001</v>
+        <v>98.26800000000001</v>
       </c>
       <c r="G58">
         <v>9.31</v>
@@ -6037,37 +6037,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M58">
-        <v>22.7650752</v>
+        <v>23.1715944</v>
       </c>
       <c r="N58">
-        <v>-16.39840853333333</v>
+        <v>-16.80492773333334</v>
       </c>
       <c r="O58">
-        <v>-3.607649877333334</v>
+        <v>-3.697084101333334</v>
       </c>
       <c r="P58">
-        <v>-12.790758656</v>
+        <v>-13.107843632</v>
       </c>
       <c r="Q58">
-        <v>-9.010758656</v>
+        <v>-9.327843632</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1946596479569228</v>
+        <v>0.1981215002349908</v>
       </c>
       <c r="T58">
-        <v>1.940140235294181</v>
+        <v>1.98525977564986</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06152699494121006</v>
+        <v>0.06044757397732917</v>
       </c>
       <c r="W58">
-        <v>0.2212919345928627</v>
+        <v>0.2215464620561458</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2796681588236821</v>
+        <v>0.2747616998969509</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2114737284730491</v>
+        <v>0.2133737284730491</v>
       </c>
       <c r="C59">
-        <v>-21.84471921127385</v>
+        <v>-24.3296692400195</v>
       </c>
       <c r="D59">
-        <v>67.11328078872616</v>
+        <v>66.35233075998052</v>
       </c>
       <c r="E59">
-        <v>64.66800000000001</v>
+        <v>66.39200000000002</v>
       </c>
       <c r="F59">
-        <v>98.26800000000001</v>
+        <v>99.99200000000002</v>
       </c>
       <c r="G59">
         <v>9.31</v>
@@ -6119,37 +6119,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M59">
-        <v>23.1715944</v>
+        <v>23.57811360000001</v>
       </c>
       <c r="N59">
-        <v>-16.80492773333334</v>
+        <v>-17.21144693333334</v>
       </c>
       <c r="O59">
-        <v>-3.697084101333334</v>
+        <v>-3.786518325333335</v>
       </c>
       <c r="P59">
-        <v>-13.107843632</v>
+        <v>-13.424928608</v>
       </c>
       <c r="Q59">
-        <v>-9.327843632</v>
+        <v>-9.644928608000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1981215002349908</v>
+        <v>0.2017482026215382</v>
       </c>
       <c r="T59">
-        <v>1.98525977564986</v>
+        <v>2.032527865546285</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06044757397732917</v>
+        <v>0.05940537442599591</v>
       </c>
       <c r="W59">
-        <v>0.2215464620561458</v>
+        <v>0.2217922127103502</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2747616998969509</v>
+        <v>0.2700244292090723</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2133737284730491</v>
+        <v>0.2152737284730491</v>
       </c>
       <c r="C60">
-        <v>-24.32966924001947</v>
+        <v>-26.79755697754577</v>
       </c>
       <c r="D60">
-        <v>66.35233075998052</v>
+        <v>65.60844302245422</v>
       </c>
       <c r="E60">
-        <v>66.392</v>
+        <v>68.11599999999999</v>
       </c>
       <c r="F60">
-        <v>99.99199999999999</v>
+        <v>101.716</v>
       </c>
       <c r="G60">
         <v>9.31</v>
@@ -6201,37 +6201,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M60">
-        <v>23.5781136</v>
+        <v>23.9846328</v>
       </c>
       <c r="N60">
-        <v>-17.21144693333333</v>
+        <v>-17.61796613333333</v>
       </c>
       <c r="O60">
-        <v>-3.786518325333333</v>
+        <v>-3.875952549333333</v>
       </c>
       <c r="P60">
-        <v>-13.424928608</v>
+        <v>-13.742013584</v>
       </c>
       <c r="Q60">
-        <v>-9.644928607999997</v>
+        <v>-9.962013583999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2017482026215381</v>
+        <v>0.2055518173196244</v>
       </c>
       <c r="T60">
-        <v>2.032527865546285</v>
+        <v>2.082101715925463</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05940537442599592</v>
+        <v>0.05839850367301293</v>
       </c>
       <c r="W60">
-        <v>0.2217922127103502</v>
+        <v>0.2220296328339036</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2700244292090724</v>
+        <v>0.2654477439682407</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2152737284730491</v>
+        <v>0.2171737284730491</v>
       </c>
       <c r="C61">
-        <v>-26.79755697754577</v>
+        <v>-29.24894992658969</v>
       </c>
       <c r="D61">
-        <v>65.60844302245422</v>
+        <v>64.88105007341031</v>
       </c>
       <c r="E61">
-        <v>68.11599999999999</v>
+        <v>69.84</v>
       </c>
       <c r="F61">
-        <v>101.716</v>
+        <v>103.44</v>
       </c>
       <c r="G61">
         <v>9.31</v>
@@ -6283,37 +6283,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M61">
-        <v>23.9846328</v>
+        <v>24.391152</v>
       </c>
       <c r="N61">
-        <v>-17.61796613333333</v>
+        <v>-18.02448533333333</v>
       </c>
       <c r="O61">
-        <v>-3.875952549333333</v>
+        <v>-3.965386773333333</v>
       </c>
       <c r="P61">
-        <v>-13.742013584</v>
+        <v>-14.05909856</v>
       </c>
       <c r="Q61">
-        <v>-9.962013583999997</v>
+        <v>-10.27909856</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2055518173196244</v>
+        <v>0.209545612752615</v>
       </c>
       <c r="T61">
-        <v>2.082101715925463</v>
+        <v>2.134154258823599</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05839850367301293</v>
+        <v>0.05742519527846272</v>
       </c>
       <c r="W61">
-        <v>0.2220296328339036</v>
+        <v>0.2222591389533385</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2654477439682407</v>
+        <v>0.2610236149021034</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2171737284730491</v>
+        <v>0.2190737284730491</v>
       </c>
       <c r="C62">
-        <v>-29.24894992658969</v>
+        <v>-31.68439069851638</v>
       </c>
       <c r="D62">
-        <v>64.88105007341031</v>
+        <v>64.16960930148362</v>
       </c>
       <c r="E62">
-        <v>69.84</v>
+        <v>71.56399999999999</v>
       </c>
       <c r="F62">
-        <v>103.44</v>
+        <v>105.164</v>
       </c>
       <c r="G62">
         <v>9.31</v>
@@ -6365,37 +6365,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M62">
-        <v>24.391152</v>
+        <v>24.7976712</v>
       </c>
       <c r="N62">
-        <v>-18.02448533333333</v>
+        <v>-18.43100453333333</v>
       </c>
       <c r="O62">
-        <v>-3.965386773333333</v>
+        <v>-4.054820997333334</v>
       </c>
       <c r="P62">
-        <v>-14.05909856</v>
+        <v>-14.376183536</v>
       </c>
       <c r="Q62">
-        <v>-10.27909856</v>
+        <v>-10.596183536</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.209545612752615</v>
+        <v>0.2137442182078103</v>
       </c>
       <c r="T62">
-        <v>2.134154258823599</v>
+        <v>2.188876162895999</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05742519527846272</v>
+        <v>0.05648379863455349</v>
       </c>
       <c r="W62">
-        <v>0.2222591389533385</v>
+        <v>0.2224811202819723</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2610236149021034</v>
+        <v>0.2567445392479705</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2190737284730491</v>
+        <v>0.2209737284730491</v>
       </c>
       <c r="C63">
-        <v>-31.68439069851638</v>
+        <v>-34.10439836322495</v>
       </c>
       <c r="D63">
-        <v>64.16960930148362</v>
+        <v>63.47360163677506</v>
       </c>
       <c r="E63">
-        <v>71.56399999999999</v>
+        <v>73.28800000000001</v>
       </c>
       <c r="F63">
-        <v>105.164</v>
+        <v>106.888</v>
       </c>
       <c r="G63">
         <v>9.31</v>
@@ -6447,37 +6447,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M63">
-        <v>24.7976712</v>
+        <v>25.2041904</v>
       </c>
       <c r="N63">
-        <v>-18.43100453333333</v>
+        <v>-18.83752373333333</v>
       </c>
       <c r="O63">
-        <v>-4.054820997333334</v>
+        <v>-4.144255221333333</v>
       </c>
       <c r="P63">
-        <v>-14.376183536</v>
+        <v>-14.693268512</v>
       </c>
       <c r="Q63">
-        <v>-10.596183536</v>
+        <v>-10.913268512</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2137442182078103</v>
+        <v>0.2181638028974895</v>
       </c>
       <c r="T63">
-        <v>2.188876162895999</v>
+        <v>2.246478167182736</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05648379863455349</v>
+        <v>0.05557276962431876</v>
       </c>
       <c r="W63">
-        <v>0.2224811202819723</v>
+        <v>0.2226959409225856</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2567445392479705</v>
+        <v>0.2526034982923581</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2209737284730491</v>
+        <v>0.2228737284730491</v>
       </c>
       <c r="C64">
-        <v>-34.10439836322495</v>
+        <v>-36.50946971214742</v>
       </c>
       <c r="D64">
-        <v>63.47360163677506</v>
+        <v>62.79253028785259</v>
       </c>
       <c r="E64">
-        <v>73.28800000000001</v>
+        <v>75.012</v>
       </c>
       <c r="F64">
-        <v>106.888</v>
+        <v>108.612</v>
       </c>
       <c r="G64">
         <v>9.31</v>
@@ -6529,37 +6529,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M64">
-        <v>25.2041904</v>
+        <v>25.6107096</v>
       </c>
       <c r="N64">
-        <v>-18.83752373333333</v>
+        <v>-19.24404293333334</v>
       </c>
       <c r="O64">
-        <v>-4.144255221333333</v>
+        <v>-4.233689445333334</v>
       </c>
       <c r="P64">
-        <v>-14.693268512</v>
+        <v>-15.010353488</v>
       </c>
       <c r="Q64">
-        <v>-10.913268512</v>
+        <v>-11.230353488</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2181638028974895</v>
+        <v>0.2228222840568811</v>
       </c>
       <c r="T64">
-        <v>2.246478167182736</v>
+        <v>2.30719379332281</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05557276962431876</v>
+        <v>0.05469066216996449</v>
       </c>
       <c r="W64">
-        <v>0.2226959409225856</v>
+        <v>0.2229039418603224</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2526034982923581</v>
+        <v>0.2485939189543841</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2228737284730491</v>
+        <v>0.2247737284730491</v>
       </c>
       <c r="C65">
-        <v>-36.50946971214742</v>
+        <v>-38.90008044079907</v>
       </c>
       <c r="D65">
-        <v>62.79253028785259</v>
+        <v>62.12591955920094</v>
       </c>
       <c r="E65">
-        <v>75.012</v>
+        <v>76.73600000000002</v>
       </c>
       <c r="F65">
-        <v>108.612</v>
+        <v>110.336</v>
       </c>
       <c r="G65">
         <v>9.31</v>
@@ -6611,37 +6611,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M65">
-        <v>25.6107096</v>
+        <v>26.01722880000001</v>
       </c>
       <c r="N65">
-        <v>-19.24404293333334</v>
+        <v>-19.65056213333334</v>
       </c>
       <c r="O65">
-        <v>-4.233689445333334</v>
+        <v>-4.323123669333334</v>
       </c>
       <c r="P65">
-        <v>-15.010353488</v>
+        <v>-15.327438464</v>
       </c>
       <c r="Q65">
-        <v>-11.230353488</v>
+        <v>-11.547438464</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2228222840568811</v>
+        <v>0.2277395697251278</v>
       </c>
       <c r="T65">
-        <v>2.30719379332281</v>
+        <v>2.371282509803999</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05469066216996449</v>
+        <v>0.05383612057355879</v>
       </c>
       <c r="W65">
-        <v>0.2229039418603224</v>
+        <v>0.2231054427687549</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2485939189543841</v>
+        <v>0.2447096389707218</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2247737284730491</v>
+        <v>0.2266737284730491</v>
       </c>
       <c r="C66">
-        <v>-38.90008044079907</v>
+        <v>-41.27668625679556</v>
       </c>
       <c r="D66">
-        <v>62.12591955920094</v>
+        <v>61.47331374320444</v>
       </c>
       <c r="E66">
-        <v>76.73600000000002</v>
+        <v>78.46000000000001</v>
       </c>
       <c r="F66">
-        <v>110.336</v>
+        <v>112.06</v>
       </c>
       <c r="G66">
         <v>9.31</v>
@@ -6693,37 +6693,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M66">
-        <v>26.01722880000001</v>
+        <v>26.423748</v>
       </c>
       <c r="N66">
-        <v>-19.65056213333334</v>
+        <v>-20.05708133333334</v>
       </c>
       <c r="O66">
-        <v>-4.323123669333334</v>
+        <v>-4.412557893333334</v>
       </c>
       <c r="P66">
-        <v>-15.327438464</v>
+        <v>-15.64452344</v>
       </c>
       <c r="Q66">
-        <v>-11.547438464</v>
+        <v>-11.86452344</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2277395697251278</v>
+        <v>0.2329378431458458</v>
       </c>
       <c r="T66">
-        <v>2.371282509803999</v>
+        <v>2.439033438655542</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05383612057355879</v>
+        <v>0.05300787256473481</v>
       </c>
       <c r="W66">
-        <v>0.2231054427687549</v>
+        <v>0.2233007436492356</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2447096389707218</v>
+        <v>0.2409448752942492</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2266737284730491</v>
+        <v>0.2285737284730491</v>
       </c>
       <c r="C67">
-        <v>-41.27668625679556</v>
+        <v>-43.63972391876081</v>
       </c>
       <c r="D67">
-        <v>61.47331374320444</v>
+        <v>60.8342760812392</v>
       </c>
       <c r="E67">
-        <v>78.46000000000001</v>
+        <v>80.184</v>
       </c>
       <c r="F67">
-        <v>112.06</v>
+        <v>113.784</v>
       </c>
       <c r="G67">
         <v>9.31</v>
@@ -6775,37 +6775,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M67">
-        <v>26.423748</v>
+        <v>26.8302672</v>
       </c>
       <c r="N67">
-        <v>-20.05708133333334</v>
+        <v>-20.46360053333333</v>
       </c>
       <c r="O67">
-        <v>-4.412557893333334</v>
+        <v>-4.501992117333334</v>
       </c>
       <c r="P67">
-        <v>-15.64452344</v>
+        <v>-15.961608416</v>
       </c>
       <c r="Q67">
-        <v>-11.86452344</v>
+        <v>-12.181608416</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2329378431458458</v>
+        <v>0.2384418973560177</v>
       </c>
       <c r="T67">
-        <v>2.439033438655542</v>
+        <v>2.510769716263058</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05300787256473481</v>
+        <v>0.05220472298042065</v>
       </c>
       <c r="W67">
-        <v>0.2233007436492356</v>
+        <v>0.2234901263212168</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2409448752942492</v>
+        <v>0.2372941953655484</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2285737284730491</v>
+        <v>0.2304737284730491</v>
       </c>
       <c r="C68">
-        <v>-43.63972391876081</v>
+        <v>-45.9896122111024</v>
       </c>
       <c r="D68">
-        <v>60.8342760812392</v>
+        <v>60.20838778889761</v>
       </c>
       <c r="E68">
-        <v>80.184</v>
+        <v>81.90800000000002</v>
       </c>
       <c r="F68">
-        <v>113.784</v>
+        <v>115.508</v>
       </c>
       <c r="G68">
         <v>9.31</v>
@@ -6857,37 +6857,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M68">
-        <v>26.8302672</v>
+        <v>27.2367864</v>
       </c>
       <c r="N68">
-        <v>-20.46360053333333</v>
+        <v>-20.87011973333334</v>
       </c>
       <c r="O68">
-        <v>-4.501992117333334</v>
+        <v>-4.591426341333334</v>
       </c>
       <c r="P68">
-        <v>-15.961608416</v>
+        <v>-16.278693392</v>
       </c>
       <c r="Q68">
-        <v>-12.181608416</v>
+        <v>-12.498693392</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2384418973560177</v>
+        <v>0.2442795306092304</v>
       </c>
       <c r="T68">
-        <v>2.510769716263058</v>
+        <v>2.586853647058908</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05220472298042065</v>
+        <v>0.05142554801056363</v>
       </c>
       <c r="W68">
-        <v>0.2234901263212168</v>
+        <v>0.2236738557791091</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2372941953655484</v>
+        <v>0.2337524909571074</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2304737284730491</v>
+        <v>0.2323737284730492</v>
       </c>
       <c r="C69">
-        <v>-45.9896122111024</v>
+        <v>-48.32675285922657</v>
       </c>
       <c r="D69">
-        <v>60.20838778889761</v>
+        <v>59.59524714077344</v>
       </c>
       <c r="E69">
-        <v>81.90800000000002</v>
+        <v>83.63200000000001</v>
       </c>
       <c r="F69">
-        <v>115.508</v>
+        <v>117.232</v>
       </c>
       <c r="G69">
         <v>9.31</v>
@@ -6939,37 +6939,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M69">
-        <v>27.2367864</v>
+        <v>27.64330560000001</v>
       </c>
       <c r="N69">
-        <v>-20.87011973333334</v>
+        <v>-21.27663893333334</v>
       </c>
       <c r="O69">
-        <v>-4.591426341333334</v>
+        <v>-4.680860565333334</v>
       </c>
       <c r="P69">
-        <v>-16.278693392</v>
+        <v>-16.595778368</v>
       </c>
       <c r="Q69">
-        <v>-12.498693392</v>
+        <v>-12.815778368</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2442795306092304</v>
+        <v>0.2504820159407689</v>
       </c>
       <c r="T69">
-        <v>2.586853647058908</v>
+        <v>2.6676928235295</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05142554801056363</v>
+        <v>0.05066928995158475</v>
       </c>
       <c r="W69">
-        <v>0.2236738557791091</v>
+        <v>0.2238521814294163</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2337524909571074</v>
+        <v>0.2303149543253853</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2323737284730492</v>
+        <v>0.2342737284730491</v>
       </c>
       <c r="C70">
-        <v>-48.32675285922657</v>
+        <v>-50.65153138939536</v>
       </c>
       <c r="D70">
-        <v>59.59524714077344</v>
+        <v>58.99446861060466</v>
       </c>
       <c r="E70">
-        <v>83.63200000000001</v>
+        <v>85.35600000000002</v>
       </c>
       <c r="F70">
-        <v>117.232</v>
+        <v>118.956</v>
       </c>
       <c r="G70">
         <v>9.31</v>
@@ -7021,37 +7021,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M70">
-        <v>27.64330560000001</v>
+        <v>28.04982480000001</v>
       </c>
       <c r="N70">
-        <v>-21.27663893333334</v>
+        <v>-21.68315813333334</v>
       </c>
       <c r="O70">
-        <v>-4.680860565333334</v>
+        <v>-4.770294789333335</v>
       </c>
       <c r="P70">
-        <v>-16.595778368</v>
+        <v>-16.91286334400001</v>
       </c>
       <c r="Q70">
-        <v>-12.815778368</v>
+        <v>-13.132863344</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2504820159407689</v>
+        <v>0.2570846616162776</v>
       </c>
       <c r="T70">
-        <v>2.6676928235295</v>
+        <v>2.753747430740129</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05066928995158475</v>
+        <v>0.04993495241605453</v>
       </c>
       <c r="W70">
-        <v>0.2238521814294163</v>
+        <v>0.2240253382202944</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2303149543253853</v>
+        <v>0.2269770564366115</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2342737284730491</v>
+        <v>0.2361737284730491</v>
       </c>
       <c r="C71">
-        <v>-50.65153138939536</v>
+        <v>-52.96431793709392</v>
       </c>
       <c r="D71">
-        <v>58.99446861060466</v>
+        <v>58.4056820629061</v>
       </c>
       <c r="E71">
-        <v>85.35600000000002</v>
+        <v>87.08000000000001</v>
       </c>
       <c r="F71">
-        <v>118.956</v>
+        <v>120.68</v>
       </c>
       <c r="G71">
         <v>9.31</v>
@@ -7103,37 +7103,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M71">
-        <v>28.04982480000001</v>
+        <v>28.456344</v>
       </c>
       <c r="N71">
-        <v>-21.68315813333334</v>
+        <v>-22.08967733333334</v>
       </c>
       <c r="O71">
-        <v>-4.770294789333335</v>
+        <v>-4.859729013333334</v>
       </c>
       <c r="P71">
-        <v>-16.91286334400001</v>
+        <v>-17.22994832000001</v>
       </c>
       <c r="Q71">
-        <v>-13.132863344</v>
+        <v>-13.44994832</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2570846616162776</v>
+        <v>0.2641274836701534</v>
       </c>
       <c r="T71">
-        <v>2.753747430740129</v>
+        <v>2.845539011764799</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04993495241605453</v>
+        <v>0.04922159595296804</v>
       </c>
       <c r="W71">
-        <v>0.2240253382202944</v>
+        <v>0.2241935476742901</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2269770564366115</v>
+        <v>0.2237345270589457</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2361737284730491</v>
+        <v>0.2380737284730491</v>
       </c>
       <c r="C72">
-        <v>-52.96431793709392</v>
+        <v>-55.26546800746911</v>
       </c>
       <c r="D72">
-        <v>58.4056820629061</v>
+        <v>57.8285319925309</v>
       </c>
       <c r="E72">
-        <v>87.08000000000001</v>
+        <v>88.804</v>
       </c>
       <c r="F72">
-        <v>120.68</v>
+        <v>122.404</v>
       </c>
       <c r="G72">
         <v>9.31</v>
@@ -7185,37 +7185,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M72">
-        <v>28.456344</v>
+        <v>28.8628632</v>
       </c>
       <c r="N72">
-        <v>-22.08967733333334</v>
+        <v>-22.49619653333334</v>
       </c>
       <c r="O72">
-        <v>-4.859729013333334</v>
+        <v>-4.949163237333334</v>
       </c>
       <c r="P72">
-        <v>-17.22994832000001</v>
+        <v>-17.547033296</v>
       </c>
       <c r="Q72">
-        <v>-13.44994832</v>
+        <v>-13.767033296</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2641274836701534</v>
+        <v>0.2716560175898139</v>
       </c>
       <c r="T72">
-        <v>2.845539011764799</v>
+        <v>2.943661046653241</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04922159595296804</v>
+        <v>0.04852833403813751</v>
       </c>
       <c r="W72">
-        <v>0.2241935476742901</v>
+        <v>0.2243570188338072</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2237345270589457</v>
+        <v>0.2205833365369887</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2380737284730491</v>
+        <v>0.2399737284730491</v>
       </c>
       <c r="C73">
-        <v>-55.26546800746908</v>
+        <v>-57.55532319112265</v>
       </c>
       <c r="D73">
-        <v>57.82853199253091</v>
+        <v>57.26267680887735</v>
       </c>
       <c r="E73">
-        <v>88.804</v>
+        <v>90.52799999999999</v>
       </c>
       <c r="F73">
-        <v>122.404</v>
+        <v>124.128</v>
       </c>
       <c r="G73">
         <v>9.31</v>
@@ -7267,37 +7267,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M73">
-        <v>28.8628632</v>
+        <v>29.2693824</v>
       </c>
       <c r="N73">
-        <v>-22.49619653333333</v>
+        <v>-22.90271573333333</v>
       </c>
       <c r="O73">
-        <v>-4.949163237333333</v>
+        <v>-5.038597461333334</v>
       </c>
       <c r="P73">
-        <v>-17.547033296</v>
+        <v>-17.864118272</v>
       </c>
       <c r="Q73">
-        <v>-13.767033296</v>
+        <v>-14.084118272</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2716560175898138</v>
+        <v>0.2797223039323072</v>
       </c>
       <c r="T73">
-        <v>2.94366104665324</v>
+        <v>3.048791798319427</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04852833403813751</v>
+        <v>0.04785432939871893</v>
       </c>
       <c r="W73">
-        <v>0.2243570188338072</v>
+        <v>0.2245159491277821</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2205833365369887</v>
+        <v>0.2175196790850861</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2399737284730491</v>
+        <v>0.2418737284730491</v>
       </c>
       <c r="C74">
-        <v>-57.55532319112265</v>
+        <v>-59.8342118382869</v>
       </c>
       <c r="D74">
-        <v>57.26267680887735</v>
+        <v>56.7077881617131</v>
       </c>
       <c r="E74">
-        <v>90.52799999999999</v>
+        <v>92.25200000000001</v>
       </c>
       <c r="F74">
-        <v>124.128</v>
+        <v>125.852</v>
       </c>
       <c r="G74">
         <v>9.31</v>
@@ -7349,37 +7349,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M74">
-        <v>29.2693824</v>
+        <v>29.6759016</v>
       </c>
       <c r="N74">
-        <v>-22.90271573333333</v>
+        <v>-23.30923493333334</v>
       </c>
       <c r="O74">
-        <v>-5.038597461333334</v>
+        <v>-5.128031685333334</v>
       </c>
       <c r="P74">
-        <v>-17.864118272</v>
+        <v>-18.181203248</v>
       </c>
       <c r="Q74">
-        <v>-14.084118272</v>
+        <v>-14.401203248</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2797223039323072</v>
+        <v>0.288386092966837</v>
       </c>
       <c r="T74">
-        <v>3.048791798319427</v>
+        <v>3.161710013071998</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04785432939871893</v>
+        <v>0.04719879063983237</v>
       </c>
       <c r="W74">
-        <v>0.2245159491277821</v>
+        <v>0.2246705251671275</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2175196790850861</v>
+        <v>0.2145399574537835</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2418737284730491</v>
+        <v>0.2437737284730491</v>
       </c>
       <c r="C75">
-        <v>-59.8342118382869</v>
+        <v>-62.1024496941796</v>
       </c>
       <c r="D75">
-        <v>56.7077881617131</v>
+        <v>56.16355030582041</v>
       </c>
       <c r="E75">
-        <v>92.25200000000001</v>
+        <v>93.976</v>
       </c>
       <c r="F75">
-        <v>125.852</v>
+        <v>127.576</v>
       </c>
       <c r="G75">
         <v>9.31</v>
@@ -7431,37 +7431,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M75">
-        <v>29.6759016</v>
+        <v>30.0824208</v>
       </c>
       <c r="N75">
-        <v>-23.30923493333334</v>
+        <v>-23.71575413333333</v>
       </c>
       <c r="O75">
-        <v>-5.128031685333334</v>
+        <v>-5.217465909333334</v>
       </c>
       <c r="P75">
-        <v>-18.181203248</v>
+        <v>-18.498288224</v>
       </c>
       <c r="Q75">
-        <v>-14.401203248</v>
+        <v>-14.718288224</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.288386092966837</v>
+        <v>0.2977163273117154</v>
       </c>
       <c r="T75">
-        <v>3.161710013071998</v>
+        <v>3.283314244343999</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04719879063983237</v>
+        <v>0.0465609691446995</v>
       </c>
       <c r="W75">
-        <v>0.2246705251671275</v>
+        <v>0.2248209234756799</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2145399574537835</v>
+        <v>0.2116407688395432</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2437737284730491</v>
+        <v>0.2456737284730491</v>
       </c>
       <c r="C76">
-        <v>-62.1024496941796</v>
+        <v>-64.36034049812011</v>
       </c>
       <c r="D76">
-        <v>56.16355030582041</v>
+        <v>55.62965950187991</v>
       </c>
       <c r="E76">
-        <v>93.976</v>
+        <v>95.70000000000002</v>
       </c>
       <c r="F76">
-        <v>127.576</v>
+        <v>129.3</v>
       </c>
       <c r="G76">
         <v>9.31</v>
@@ -7513,37 +7513,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M76">
-        <v>30.0824208</v>
+        <v>30.48894</v>
       </c>
       <c r="N76">
-        <v>-23.71575413333333</v>
+        <v>-24.12227333333334</v>
       </c>
       <c r="O76">
-        <v>-5.217465909333334</v>
+        <v>-5.306900133333334</v>
       </c>
       <c r="P76">
-        <v>-18.498288224</v>
+        <v>-18.8153732</v>
       </c>
       <c r="Q76">
-        <v>-14.718288224</v>
+        <v>-15.0353732</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2977163273117154</v>
+        <v>0.3077929804041841</v>
       </c>
       <c r="T76">
-        <v>3.283314244343999</v>
+        <v>3.414646814117759</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0465609691446995</v>
+        <v>0.04594015622277017</v>
       </c>
       <c r="W76">
-        <v>0.2248209234756799</v>
+        <v>0.2249673111626708</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2116407688395432</v>
+        <v>0.2088188919216827</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2456737284730491</v>
+        <v>0.2475737284730491</v>
       </c>
       <c r="C77">
-        <v>-64.36034049812011</v>
+        <v>-66.60817654879648</v>
       </c>
       <c r="D77">
-        <v>55.62965950187991</v>
+        <v>55.10582345120353</v>
       </c>
       <c r="E77">
-        <v>95.70000000000002</v>
+        <v>97.42400000000001</v>
       </c>
       <c r="F77">
-        <v>129.3</v>
+        <v>131.024</v>
       </c>
       <c r="G77">
         <v>9.31</v>
@@ -7595,37 +7595,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M77">
-        <v>30.48894</v>
+        <v>30.8954592</v>
       </c>
       <c r="N77">
-        <v>-24.12227333333334</v>
+        <v>-24.52879253333333</v>
       </c>
       <c r="O77">
-        <v>-5.306900133333334</v>
+        <v>-5.396334357333333</v>
       </c>
       <c r="P77">
-        <v>-18.8153732</v>
+        <v>-19.132458176</v>
       </c>
       <c r="Q77">
-        <v>-15.0353732</v>
+        <v>-15.352458176</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3077929804041841</v>
+        <v>0.3187093545876918</v>
       </c>
       <c r="T77">
-        <v>3.414646814117759</v>
+        <v>3.556923764706</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04594015622277017</v>
+        <v>0.04533568048299688</v>
       </c>
       <c r="W77">
-        <v>0.2249673111626708</v>
+        <v>0.2251098465421094</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2088188919216827</v>
+        <v>0.2060712749227132</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2475737284730491</v>
+        <v>0.2494737284730491</v>
       </c>
       <c r="C78">
-        <v>-66.60817654879648</v>
+        <v>-68.84623923789357</v>
       </c>
       <c r="D78">
-        <v>55.10582345120353</v>
+        <v>54.59176076210644</v>
       </c>
       <c r="E78">
-        <v>97.42400000000001</v>
+        <v>99.14800000000002</v>
       </c>
       <c r="F78">
-        <v>131.024</v>
+        <v>132.748</v>
       </c>
       <c r="G78">
         <v>9.31</v>
@@ -7677,37 +7677,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M78">
-        <v>30.8954592</v>
+        <v>31.30197840000001</v>
       </c>
       <c r="N78">
-        <v>-24.52879253333333</v>
+        <v>-24.93531173333334</v>
       </c>
       <c r="O78">
-        <v>-5.396334357333333</v>
+        <v>-5.485768581333335</v>
       </c>
       <c r="P78">
-        <v>-19.132458176</v>
+        <v>-19.449543152</v>
       </c>
       <c r="Q78">
-        <v>-15.352458176</v>
+        <v>-15.669543152</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3187093545876918</v>
+        <v>0.3305749787002001</v>
       </c>
       <c r="T78">
-        <v>3.556923764706</v>
+        <v>3.711572624041042</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04533568048299688</v>
+        <v>0.04474690541178912</v>
       </c>
       <c r="W78">
-        <v>0.2251098465421094</v>
+        <v>0.2252486797039001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2060712749227132</v>
+        <v>0.2033950245990415</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2494737284730491</v>
+        <v>0.2513737284730491</v>
       </c>
       <c r="C79">
-        <v>-68.84623923789357</v>
+        <v>-71.07479955412873</v>
       </c>
       <c r="D79">
-        <v>54.59176076210644</v>
+        <v>54.08720044587128</v>
       </c>
       <c r="E79">
-        <v>99.14800000000002</v>
+        <v>100.872</v>
       </c>
       <c r="F79">
-        <v>132.748</v>
+        <v>134.472</v>
       </c>
       <c r="G79">
         <v>9.31</v>
@@ -7759,37 +7759,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M79">
-        <v>31.30197840000001</v>
+        <v>31.7084976</v>
       </c>
       <c r="N79">
-        <v>-24.93531173333334</v>
+        <v>-25.34183093333334</v>
       </c>
       <c r="O79">
-        <v>-5.485768581333335</v>
+        <v>-5.575202805333334</v>
       </c>
       <c r="P79">
-        <v>-19.449543152</v>
+        <v>-19.766628128</v>
       </c>
       <c r="Q79">
-        <v>-15.669543152</v>
+        <v>-15.986628128</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3305749787002001</v>
+        <v>0.3435192959138456</v>
       </c>
       <c r="T79">
-        <v>3.711572624041042</v>
+        <v>3.880280470588362</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04474690541178912</v>
+        <v>0.04417322713727901</v>
       </c>
       <c r="W79">
-        <v>0.2252486797039001</v>
+        <v>0.2253839530410296</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2033950245990415</v>
+        <v>0.200787396078541</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2513737284730491</v>
+        <v>0.2532737284730491</v>
       </c>
       <c r="C80">
-        <v>-71.07479955412873</v>
+        <v>-73.2941185595926</v>
       </c>
       <c r="D80">
-        <v>54.08720044587128</v>
+        <v>53.59188144040739</v>
       </c>
       <c r="E80">
-        <v>100.872</v>
+        <v>102.596</v>
       </c>
       <c r="F80">
-        <v>134.472</v>
+        <v>136.196</v>
       </c>
       <c r="G80">
         <v>9.31</v>
@@ -7841,37 +7841,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M80">
-        <v>31.7084976</v>
+        <v>32.1150168</v>
       </c>
       <c r="N80">
-        <v>-25.34183093333334</v>
+        <v>-25.74835013333333</v>
       </c>
       <c r="O80">
-        <v>-5.575202805333334</v>
+        <v>-5.664637029333333</v>
       </c>
       <c r="P80">
-        <v>-19.766628128</v>
+        <v>-20.083713104</v>
       </c>
       <c r="Q80">
-        <v>-15.986628128</v>
+        <v>-16.303713104</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3435192959138456</v>
+        <v>0.3576964052430763</v>
       </c>
       <c r="T80">
-        <v>3.880280470588362</v>
+        <v>4.065055731092571</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04417322713727901</v>
+        <v>0.04361407236338941</v>
       </c>
       <c r="W80">
-        <v>0.2253839530410296</v>
+        <v>0.2255158017367128</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.200787396078541</v>
+        <v>0.1982457834699519</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2532737284730491</v>
+        <v>0.2551737284730491</v>
       </c>
       <c r="C81">
-        <v>-73.2941185595926</v>
+        <v>-75.5044478401541</v>
       </c>
       <c r="D81">
-        <v>53.59188144040739</v>
+        <v>53.10555215984591</v>
       </c>
       <c r="E81">
-        <v>102.596</v>
+        <v>104.32</v>
       </c>
       <c r="F81">
-        <v>136.196</v>
+        <v>137.92</v>
       </c>
       <c r="G81">
         <v>9.31</v>
@@ -7923,37 +7923,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M81">
-        <v>32.1150168</v>
+        <v>32.521536</v>
       </c>
       <c r="N81">
-        <v>-25.74835013333333</v>
+        <v>-26.15486933333334</v>
       </c>
       <c r="O81">
-        <v>-5.664637029333333</v>
+        <v>-5.754071253333334</v>
       </c>
       <c r="P81">
-        <v>-20.083713104</v>
+        <v>-20.40079808</v>
       </c>
       <c r="Q81">
-        <v>-16.303713104</v>
+        <v>-16.62079808</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3576964052430763</v>
+        <v>0.3732912255052301</v>
       </c>
       <c r="T81">
-        <v>4.065055731092571</v>
+        <v>4.268308517647199</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04361407236338941</v>
+        <v>0.04306889645884703</v>
       </c>
       <c r="W81">
-        <v>0.2255158017367128</v>
+        <v>0.2256443542150039</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1982457834699519</v>
+        <v>0.1957677111765774</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2551737284730491</v>
+        <v>0.2570737284730492</v>
       </c>
       <c r="C82">
-        <v>-75.5044478401541</v>
+        <v>-77.70602993156203</v>
       </c>
       <c r="D82">
-        <v>53.10555215984591</v>
+        <v>52.62797006843797</v>
       </c>
       <c r="E82">
-        <v>104.32</v>
+        <v>106.044</v>
       </c>
       <c r="F82">
-        <v>137.92</v>
+        <v>139.644</v>
       </c>
       <c r="G82">
         <v>9.31</v>
@@ -8005,37 +8005,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M82">
-        <v>32.521536</v>
+        <v>32.9280552</v>
       </c>
       <c r="N82">
-        <v>-26.15486933333334</v>
+        <v>-26.56138853333334</v>
       </c>
       <c r="O82">
-        <v>-5.754071253333334</v>
+        <v>-5.843505477333334</v>
       </c>
       <c r="P82">
-        <v>-20.40079808</v>
+        <v>-20.717883056</v>
       </c>
       <c r="Q82">
-        <v>-16.62079808</v>
+        <v>-16.937883056</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3732912255052301</v>
+        <v>0.3905276057949791</v>
       </c>
       <c r="T82">
-        <v>4.268308517647199</v>
+        <v>4.492956334365473</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04306889645884703</v>
+        <v>0.04253718168775016</v>
       </c>
       <c r="W82">
-        <v>0.2256443542150039</v>
+        <v>0.2257697325580285</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1957677111765774</v>
+        <v>0.1933508258534099</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2570737284730492</v>
+        <v>0.2589737284730492</v>
       </c>
       <c r="C83">
-        <v>-77.70602993156203</v>
+        <v>-79.89909872276007</v>
       </c>
       <c r="D83">
-        <v>52.62797006843797</v>
+        <v>52.15890127723994</v>
       </c>
       <c r="E83">
-        <v>106.044</v>
+        <v>107.768</v>
       </c>
       <c r="F83">
-        <v>139.644</v>
+        <v>141.368</v>
       </c>
       <c r="G83">
         <v>9.31</v>
@@ -8087,37 +8087,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M83">
-        <v>32.9280552</v>
+        <v>33.33457440000001</v>
       </c>
       <c r="N83">
-        <v>-26.56138853333334</v>
+        <v>-26.96790773333334</v>
       </c>
       <c r="O83">
-        <v>-5.843505477333334</v>
+        <v>-5.932939701333335</v>
       </c>
       <c r="P83">
-        <v>-20.717883056</v>
+        <v>-21.03496803200001</v>
       </c>
       <c r="Q83">
-        <v>-16.937883056</v>
+        <v>-17.254968032</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3905276057949791</v>
+        <v>0.4096791394502559</v>
       </c>
       <c r="T83">
-        <v>4.492956334365473</v>
+        <v>4.742565019608</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04253718168775016</v>
+        <v>0.04201843556960686</v>
       </c>
       <c r="W83">
-        <v>0.2257697325580285</v>
+        <v>0.2258920528926867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1933508258534099</v>
+        <v>0.1909928889527585</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2589737284730492</v>
+        <v>0.2608737284730491</v>
       </c>
       <c r="C84">
-        <v>-79.89909872276007</v>
+        <v>-82.08387983782393</v>
       </c>
       <c r="D84">
-        <v>52.15890127723994</v>
+        <v>51.69812016217608</v>
       </c>
       <c r="E84">
-        <v>107.768</v>
+        <v>109.492</v>
       </c>
       <c r="F84">
-        <v>141.368</v>
+        <v>143.092</v>
       </c>
       <c r="G84">
         <v>9.31</v>
@@ -8169,37 +8169,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M84">
-        <v>33.33457440000001</v>
+        <v>33.74109360000001</v>
       </c>
       <c r="N84">
-        <v>-26.96790773333334</v>
+        <v>-27.37442693333334</v>
       </c>
       <c r="O84">
-        <v>-5.932939701333335</v>
+        <v>-6.022373925333334</v>
       </c>
       <c r="P84">
-        <v>-21.03496803200001</v>
+        <v>-21.35205300800001</v>
       </c>
       <c r="Q84">
-        <v>-17.254968032</v>
+        <v>-17.572053008</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4096791394502559</v>
+        <v>0.4310837947120356</v>
       </c>
       <c r="T84">
-        <v>4.742565019608</v>
+        <v>5.021539432526118</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04201843556960686</v>
+        <v>0.04151218935792485</v>
       </c>
       <c r="W84">
-        <v>0.2258920528926867</v>
+        <v>0.2260114257494013</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1909928889527585</v>
+        <v>0.1886917698087494</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2608737284730491</v>
+        <v>0.2627737284730491</v>
       </c>
       <c r="C85">
-        <v>-82.08387983782393</v>
+        <v>-84.2605909978312</v>
       </c>
       <c r="D85">
-        <v>51.69812016217608</v>
+        <v>51.24540900216882</v>
       </c>
       <c r="E85">
-        <v>109.492</v>
+        <v>111.216</v>
       </c>
       <c r="F85">
-        <v>143.092</v>
+        <v>144.816</v>
       </c>
       <c r="G85">
         <v>9.31</v>
@@ -8251,37 +8251,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M85">
-        <v>33.74109360000001</v>
+        <v>34.14761280000001</v>
       </c>
       <c r="N85">
-        <v>-27.37442693333334</v>
+        <v>-27.78094613333334</v>
       </c>
       <c r="O85">
-        <v>-6.022373925333334</v>
+        <v>-6.111808149333336</v>
       </c>
       <c r="P85">
-        <v>-21.35205300800001</v>
+        <v>-21.66913798400001</v>
       </c>
       <c r="Q85">
-        <v>-17.572053008</v>
+        <v>-17.88913798400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4310837947120356</v>
+        <v>0.4551640318815378</v>
       </c>
       <c r="T85">
-        <v>5.021539432526118</v>
+        <v>5.335385647059001</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04151218935792485</v>
+        <v>0.04101799662747336</v>
       </c>
       <c r="W85">
-        <v>0.2260114257494013</v>
+        <v>0.2261279563952418</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1886917698087494</v>
+        <v>0.186445439215788</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2627737284730491</v>
+        <v>0.2646737284730491</v>
       </c>
       <c r="C86">
-        <v>-84.26059099783117</v>
+        <v>-86.42944236388313</v>
       </c>
       <c r="D86">
-        <v>51.24540900216882</v>
+        <v>50.80055763611686</v>
       </c>
       <c r="E86">
-        <v>111.216</v>
+        <v>112.94</v>
       </c>
       <c r="F86">
-        <v>144.816</v>
+        <v>146.54</v>
       </c>
       <c r="G86">
         <v>9.31</v>
@@ -8333,37 +8333,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M86">
-        <v>34.1476128</v>
+        <v>34.554132</v>
       </c>
       <c r="N86">
-        <v>-27.78094613333334</v>
+        <v>-28.18746533333334</v>
       </c>
       <c r="O86">
-        <v>-6.111808149333334</v>
+        <v>-6.201242373333334</v>
       </c>
       <c r="P86">
-        <v>-21.669137984</v>
+        <v>-21.98622296</v>
       </c>
       <c r="Q86">
-        <v>-17.889137984</v>
+        <v>-18.20622296</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4551640318815375</v>
+        <v>0.4824549673403067</v>
       </c>
       <c r="T86">
-        <v>5.335385647058997</v>
+        <v>5.691078023529597</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04101799662747337</v>
+        <v>0.0405354319612678</v>
       </c>
       <c r="W86">
-        <v>0.2261279563952418</v>
+        <v>0.226241745143533</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.186445439215788</v>
+        <v>0.1842519634603083</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2646737284730491</v>
+        <v>0.2665737284730492</v>
       </c>
       <c r="C87">
-        <v>-86.42944236388313</v>
+        <v>-88.59063686241429</v>
       </c>
       <c r="D87">
-        <v>50.80055763611686</v>
+        <v>50.36336313758572</v>
       </c>
       <c r="E87">
-        <v>112.94</v>
+        <v>114.664</v>
       </c>
       <c r="F87">
-        <v>146.54</v>
+        <v>148.264</v>
       </c>
       <c r="G87">
         <v>9.31</v>
@@ -8415,37 +8415,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M87">
-        <v>34.554132</v>
+        <v>34.9606512</v>
       </c>
       <c r="N87">
-        <v>-28.18746533333334</v>
+        <v>-28.59398453333333</v>
       </c>
       <c r="O87">
-        <v>-6.201242373333334</v>
+        <v>-6.290676597333333</v>
       </c>
       <c r="P87">
-        <v>-21.98622296</v>
+        <v>-22.303307936</v>
       </c>
       <c r="Q87">
-        <v>-18.20622296</v>
+        <v>-18.523307936</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4824549673403067</v>
+        <v>0.5136446078646144</v>
       </c>
       <c r="T87">
-        <v>5.691078023529597</v>
+        <v>6.097583596638855</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0405354319612678</v>
+        <v>0.04006408972916004</v>
       </c>
       <c r="W87">
-        <v>0.226241745143533</v>
+        <v>0.2263528876418641</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1842519634603083</v>
+        <v>0.1821094987689093</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2665737284730492</v>
+        <v>0.2684737284730491</v>
       </c>
       <c r="C88">
-        <v>-88.59063686241429</v>
+        <v>-90.7443704938471</v>
       </c>
       <c r="D88">
-        <v>50.36336313758572</v>
+        <v>49.9336295061529</v>
       </c>
       <c r="E88">
-        <v>114.664</v>
+        <v>116.388</v>
       </c>
       <c r="F88">
-        <v>148.264</v>
+        <v>149.988</v>
       </c>
       <c r="G88">
         <v>9.31</v>
@@ -8497,37 +8497,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M88">
-        <v>34.9606512</v>
+        <v>35.3671704</v>
       </c>
       <c r="N88">
-        <v>-28.59398453333333</v>
+        <v>-29.00050373333333</v>
       </c>
       <c r="O88">
-        <v>-6.290676597333333</v>
+        <v>-6.380110821333333</v>
       </c>
       <c r="P88">
-        <v>-22.303307936</v>
+        <v>-22.620392912</v>
       </c>
       <c r="Q88">
-        <v>-18.523307936</v>
+        <v>-18.840392912</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5136446078646144</v>
+        <v>0.5496326546234308</v>
       </c>
       <c r="T88">
-        <v>6.097583596638855</v>
+        <v>6.566628488687997</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04006408972916004</v>
+        <v>0.03960358295066395</v>
       </c>
       <c r="W88">
-        <v>0.2263528876418641</v>
+        <v>0.2264614751402335</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1821094987689093</v>
+        <v>0.1800162861393816</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2684737284730491</v>
+        <v>0.2703737284730491</v>
       </c>
       <c r="C89">
-        <v>-90.7443704938471</v>
+        <v>-92.89083262557897</v>
       </c>
       <c r="D89">
-        <v>49.9336295061529</v>
+        <v>49.51116737442105</v>
       </c>
       <c r="E89">
-        <v>116.388</v>
+        <v>118.112</v>
       </c>
       <c r="F89">
-        <v>149.988</v>
+        <v>151.712</v>
       </c>
       <c r="G89">
         <v>9.31</v>
@@ -8579,37 +8579,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M89">
-        <v>35.3671704</v>
+        <v>35.7736896</v>
       </c>
       <c r="N89">
-        <v>-29.00050373333333</v>
+        <v>-29.40702293333334</v>
       </c>
       <c r="O89">
-        <v>-6.380110821333333</v>
+        <v>-6.469545045333335</v>
       </c>
       <c r="P89">
-        <v>-22.620392912</v>
+        <v>-22.937477888</v>
       </c>
       <c r="Q89">
-        <v>-18.840392912</v>
+        <v>-19.157477888</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5496326546234308</v>
+        <v>0.5916187091753835</v>
       </c>
       <c r="T89">
-        <v>6.566628488687997</v>
+        <v>7.113847529411998</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03960358295066395</v>
+        <v>0.03915354223531549</v>
       </c>
       <c r="W89">
-        <v>0.2264614751402335</v>
+        <v>0.2265675947409126</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1800162861393816</v>
+        <v>0.1779706465241613</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2703737284730491</v>
+        <v>0.2722737284730491</v>
       </c>
       <c r="C90">
-        <v>-92.89083262557897</v>
+        <v>-95.03020627022045</v>
       </c>
       <c r="D90">
-        <v>49.51116737442105</v>
+        <v>49.09579372977955</v>
       </c>
       <c r="E90">
-        <v>118.112</v>
+        <v>119.836</v>
       </c>
       <c r="F90">
-        <v>151.712</v>
+        <v>153.436</v>
       </c>
       <c r="G90">
         <v>9.31</v>
@@ -8661,37 +8661,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M90">
-        <v>35.7736896</v>
+        <v>36.1802088</v>
       </c>
       <c r="N90">
-        <v>-29.40702293333334</v>
+        <v>-29.81354213333334</v>
       </c>
       <c r="O90">
-        <v>-6.469545045333335</v>
+        <v>-6.558979269333334</v>
       </c>
       <c r="P90">
-        <v>-22.937477888</v>
+        <v>-23.254562864</v>
       </c>
       <c r="Q90">
-        <v>-19.157477888</v>
+        <v>-19.474562864</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5916187091753835</v>
+        <v>0.6412385918276912</v>
       </c>
       <c r="T90">
-        <v>7.113847529411998</v>
+        <v>7.760560941176727</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03915354223531549</v>
+        <v>0.03871361479446925</v>
       </c>
       <c r="W90">
-        <v>0.2265675947409126</v>
+        <v>0.2266713296314642</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1779706465241613</v>
+        <v>0.1759709763384966</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2722737284730491</v>
+        <v>0.2741737284730491</v>
       </c>
       <c r="C91">
-        <v>-95.03020627022045</v>
+        <v>-97.16266834994511</v>
       </c>
       <c r="D91">
-        <v>49.09579372977955</v>
+        <v>48.68733165005488</v>
       </c>
       <c r="E91">
-        <v>119.836</v>
+        <v>121.56</v>
       </c>
       <c r="F91">
-        <v>153.436</v>
+        <v>155.16</v>
       </c>
       <c r="G91">
         <v>9.31</v>
@@ -8743,37 +8743,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M91">
-        <v>36.1802088</v>
+        <v>36.586728</v>
       </c>
       <c r="N91">
-        <v>-29.81354213333334</v>
+        <v>-30.22006133333333</v>
       </c>
       <c r="O91">
-        <v>-6.558979269333334</v>
+        <v>-6.648413493333334</v>
       </c>
       <c r="P91">
-        <v>-23.254562864</v>
+        <v>-23.57164784</v>
       </c>
       <c r="Q91">
-        <v>-19.474562864</v>
+        <v>-19.79164784</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6412385918276912</v>
+        <v>0.7007824510104602</v>
       </c>
       <c r="T91">
-        <v>7.760560941176727</v>
+        <v>8.536617035294398</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03871361479446925</v>
+        <v>0.03828346351897514</v>
       </c>
       <c r="W91">
-        <v>0.2266713296314642</v>
+        <v>0.2267727593022257</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1759709763384966</v>
+        <v>0.1740157432680689</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2741737284730491</v>
+        <v>0.2760737284730491</v>
       </c>
       <c r="C92">
-        <v>-97.16266834994511</v>
+        <v>-99.28838994775185</v>
       </c>
       <c r="D92">
-        <v>48.68733165005488</v>
+        <v>48.28561005224815</v>
       </c>
       <c r="E92">
-        <v>121.56</v>
+        <v>123.284</v>
       </c>
       <c r="F92">
-        <v>155.16</v>
+        <v>156.884</v>
       </c>
       <c r="G92">
         <v>9.31</v>
@@ -8825,37 +8825,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M92">
-        <v>36.586728</v>
+        <v>36.99324720000001</v>
       </c>
       <c r="N92">
-        <v>-30.22006133333333</v>
+        <v>-30.62658053333334</v>
       </c>
       <c r="O92">
-        <v>-6.648413493333334</v>
+        <v>-6.737847717333334</v>
       </c>
       <c r="P92">
-        <v>-23.57164784</v>
+        <v>-23.888732816</v>
       </c>
       <c r="Q92">
-        <v>-19.79164784</v>
+        <v>-20.108732816</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7007824510104602</v>
+        <v>0.7735582789005117</v>
       </c>
       <c r="T92">
-        <v>8.536617035294398</v>
+        <v>9.485130039216001</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03828346351897514</v>
+        <v>0.03786276611766772</v>
       </c>
       <c r="W92">
-        <v>0.2267727593022257</v>
+        <v>0.226871959749454</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1740157432680689</v>
+        <v>0.1721034823530351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2760737284730491</v>
+        <v>0.2779737284730491</v>
       </c>
       <c r="C93">
-        <v>-99.28838994775185</v>
+        <v>-101.40753654639</v>
       </c>
       <c r="D93">
-        <v>48.28561005224815</v>
+        <v>47.89046345360996</v>
       </c>
       <c r="E93">
-        <v>123.284</v>
+        <v>125.008</v>
       </c>
       <c r="F93">
-        <v>156.884</v>
+        <v>158.608</v>
       </c>
       <c r="G93">
         <v>9.31</v>
@@ -8907,37 +8907,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M93">
-        <v>36.99324720000001</v>
+        <v>37.3997664</v>
       </c>
       <c r="N93">
-        <v>-30.62658053333334</v>
+        <v>-31.03309973333334</v>
       </c>
       <c r="O93">
-        <v>-6.737847717333334</v>
+        <v>-6.827281941333334</v>
       </c>
       <c r="P93">
-        <v>-23.888732816</v>
+        <v>-24.205817792</v>
       </c>
       <c r="Q93">
-        <v>-20.108732816</v>
+        <v>-20.425817792</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7735582789005117</v>
+        <v>0.8645280637630756</v>
       </c>
       <c r="T93">
-        <v>9.485130039216001</v>
+        <v>10.670771294118</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03786276611766772</v>
+        <v>0.0374512143120409</v>
       </c>
       <c r="W93">
-        <v>0.226871959749454</v>
+        <v>0.2269690036652208</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1721034823530351</v>
+        <v>0.1702327923274587</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2779737284730491</v>
+        <v>0.2798737284730491</v>
       </c>
       <c r="C94">
-        <v>-101.40753654639</v>
+        <v>-103.5202682556486</v>
       </c>
       <c r="D94">
-        <v>47.89046345360996</v>
+        <v>47.50173174435138</v>
       </c>
       <c r="E94">
-        <v>125.008</v>
+        <v>126.732</v>
       </c>
       <c r="F94">
-        <v>158.608</v>
+        <v>160.332</v>
       </c>
       <c r="G94">
         <v>9.31</v>
@@ -8989,37 +8989,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M94">
-        <v>37.3997664</v>
+        <v>37.80628560000001</v>
       </c>
       <c r="N94">
-        <v>-31.03309973333334</v>
+        <v>-31.43961893333334</v>
       </c>
       <c r="O94">
-        <v>-6.827281941333334</v>
+        <v>-6.916716165333336</v>
       </c>
       <c r="P94">
-        <v>-24.205817792</v>
+        <v>-24.52290276800001</v>
       </c>
       <c r="Q94">
-        <v>-20.425817792</v>
+        <v>-20.74290276800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8645280637630756</v>
+        <v>0.9814892157292294</v>
       </c>
       <c r="T94">
-        <v>10.670771294118</v>
+        <v>12.19516719327772</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0374512143120409</v>
+        <v>0.03704851308287917</v>
       </c>
       <c r="W94">
-        <v>0.2269690036652208</v>
+        <v>0.2270639606150571</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1702327923274587</v>
+        <v>0.1684023321949053</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2798737284730491</v>
+        <v>0.2817737284730492</v>
       </c>
       <c r="C95">
-        <v>-103.5202682556486</v>
+        <v>-105.6267400286646</v>
       </c>
       <c r="D95">
-        <v>47.50173174435138</v>
+        <v>47.11925997133545</v>
       </c>
       <c r="E95">
-        <v>126.732</v>
+        <v>128.456</v>
       </c>
       <c r="F95">
-        <v>160.332</v>
+        <v>162.056</v>
       </c>
       <c r="G95">
         <v>9.31</v>
@@ -9071,37 +9071,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M95">
-        <v>37.80628560000001</v>
+        <v>38.21280480000001</v>
       </c>
       <c r="N95">
-        <v>-31.43961893333334</v>
+        <v>-31.84613813333334</v>
       </c>
       <c r="O95">
-        <v>-6.916716165333336</v>
+        <v>-7.006150389333335</v>
       </c>
       <c r="P95">
-        <v>-24.52290276800001</v>
+        <v>-24.83998774400001</v>
       </c>
       <c r="Q95">
-        <v>-20.74290276800001</v>
+        <v>-21.059987744</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9814892157292294</v>
+        <v>1.137437418350768</v>
       </c>
       <c r="T95">
-        <v>12.19516719327772</v>
+        <v>14.22769505882401</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03704851308287917</v>
+        <v>0.0366543799649762</v>
       </c>
       <c r="W95">
-        <v>0.2270639606150571</v>
+        <v>0.2271568972042586</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1684023321949053</v>
+        <v>0.1666108180226191</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2817737284730492</v>
+        <v>0.2836737284730492</v>
       </c>
       <c r="C96">
-        <v>-105.6267400286646</v>
+        <v>-107.7271018678648</v>
       </c>
       <c r="D96">
-        <v>47.11925997133545</v>
+        <v>46.74289813213519</v>
       </c>
       <c r="E96">
-        <v>128.456</v>
+        <v>130.18</v>
       </c>
       <c r="F96">
-        <v>162.056</v>
+        <v>163.78</v>
       </c>
       <c r="G96">
         <v>9.31</v>
@@ -9153,37 +9153,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M96">
-        <v>38.21280480000001</v>
+        <v>38.61932400000001</v>
       </c>
       <c r="N96">
-        <v>-31.84613813333334</v>
+        <v>-32.25265733333334</v>
       </c>
       <c r="O96">
-        <v>-7.006150389333335</v>
+        <v>-7.095584613333335</v>
       </c>
       <c r="P96">
-        <v>-24.83998774400001</v>
+        <v>-25.15707272</v>
       </c>
       <c r="Q96">
-        <v>-21.059987744</v>
+        <v>-21.37707272</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.137437418350768</v>
+        <v>1.355764902020922</v>
       </c>
       <c r="T96">
-        <v>14.22769505882401</v>
+        <v>17.07323407058882</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0366543799649762</v>
+        <v>0.0362685443863975</v>
       </c>
       <c r="W96">
-        <v>0.2271568972042586</v>
+        <v>0.2272478772336875</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1666108180226191</v>
+        <v>0.1648570199381705</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2836737284730492</v>
+        <v>0.2855737284730492</v>
       </c>
       <c r="C97">
-        <v>-107.7271018678648</v>
+        <v>-109.8214990211169</v>
       </c>
       <c r="D97">
-        <v>46.74289813213519</v>
+        <v>46.3725009788831</v>
       </c>
       <c r="E97">
-        <v>130.18</v>
+        <v>131.904</v>
       </c>
       <c r="F97">
-        <v>163.78</v>
+        <v>165.504</v>
       </c>
       <c r="G97">
         <v>9.31</v>
@@ -9235,37 +9235,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M97">
-        <v>38.61932400000001</v>
+        <v>39.0258432</v>
       </c>
       <c r="N97">
-        <v>-32.25265733333334</v>
+        <v>-32.65917653333334</v>
       </c>
       <c r="O97">
-        <v>-7.095584613333335</v>
+        <v>-7.185018837333335</v>
       </c>
       <c r="P97">
-        <v>-25.15707272</v>
+        <v>-25.474157696</v>
       </c>
       <c r="Q97">
-        <v>-21.37707272</v>
+        <v>-21.694157696</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.355764902020922</v>
+        <v>1.683256127526154</v>
       </c>
       <c r="T97">
-        <v>17.07323407058882</v>
+        <v>21.34154258823603</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0362685443863975</v>
+        <v>0.0358907470490392</v>
       </c>
       <c r="W97">
-        <v>0.2272478772336875</v>
+        <v>0.2273369618458366</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1648570199381705</v>
+        <v>0.1631397593138145</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2855737284730491</v>
+        <v>0.2874737284730491</v>
       </c>
       <c r="C98">
-        <v>-109.8214990211169</v>
+        <v>-111.9100721686268</v>
       </c>
       <c r="D98">
-        <v>46.37250097888311</v>
+        <v>46.00792783137319</v>
       </c>
       <c r="E98">
-        <v>131.904</v>
+        <v>133.628</v>
       </c>
       <c r="F98">
-        <v>165.504</v>
+        <v>167.228</v>
       </c>
       <c r="G98">
         <v>9.31</v>
@@ -9317,37 +9317,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M98">
-        <v>39.0258432</v>
+        <v>39.4323624</v>
       </c>
       <c r="N98">
-        <v>-32.65917653333333</v>
+        <v>-33.06569573333334</v>
       </c>
       <c r="O98">
-        <v>-7.185018837333333</v>
+        <v>-7.274453061333333</v>
       </c>
       <c r="P98">
-        <v>-25.474157696</v>
+        <v>-25.791242672</v>
       </c>
       <c r="Q98">
-        <v>-21.694157696</v>
+        <v>-22.011242672</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.683256127526149</v>
+        <v>2.229074836701532</v>
       </c>
       <c r="T98">
-        <v>21.34154258823597</v>
+        <v>28.45539011764797</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0358907470490392</v>
+        <v>0.03552073934750271</v>
       </c>
       <c r="W98">
-        <v>0.2273369618458366</v>
+        <v>0.2274242096618589</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1631397593138146</v>
+        <v>0.1614579061250123</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2874737284730491</v>
+        <v>0.2893737284730491</v>
       </c>
       <c r="C99">
-        <v>-111.9100721686268</v>
+        <v>-113.9929576010895</v>
       </c>
       <c r="D99">
-        <v>46.00792783137319</v>
+        <v>45.64904239891047</v>
       </c>
       <c r="E99">
-        <v>133.628</v>
+        <v>135.352</v>
       </c>
       <c r="F99">
-        <v>167.228</v>
+        <v>168.952</v>
       </c>
       <c r="G99">
         <v>9.31</v>
@@ -9399,37 +9399,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M99">
-        <v>39.4323624</v>
+        <v>39.8388816</v>
       </c>
       <c r="N99">
-        <v>-33.06569573333334</v>
+        <v>-33.47221493333333</v>
       </c>
       <c r="O99">
-        <v>-7.274453061333333</v>
+        <v>-7.363887285333333</v>
       </c>
       <c r="P99">
-        <v>-25.791242672</v>
+        <v>-26.108327648</v>
       </c>
       <c r="Q99">
-        <v>-22.011242672</v>
+        <v>-22.328327648</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.229074836701532</v>
+        <v>3.320712255052298</v>
       </c>
       <c r="T99">
-        <v>28.45539011764797</v>
+        <v>42.68308517647195</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03552073934750271</v>
+        <v>0.0351582828235486</v>
       </c>
       <c r="W99">
-        <v>0.2274242096618589</v>
+        <v>0.2275096769102072</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1614579061250123</v>
+        <v>0.1598103764706755</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2893737284730491</v>
+        <v>0.2912737284730491</v>
       </c>
       <c r="C100">
-        <v>-113.9929576010895</v>
+        <v>-116.0702873895661</v>
       </c>
       <c r="D100">
-        <v>45.64904239891047</v>
+        <v>45.29571261043392</v>
       </c>
       <c r="E100">
-        <v>135.352</v>
+        <v>137.076</v>
       </c>
       <c r="F100">
-        <v>168.952</v>
+        <v>170.676</v>
       </c>
       <c r="G100">
         <v>9.31</v>
@@ -9481,37 +9481,37 @@
         <v>6.366666666666666</v>
       </c>
       <c r="M100">
-        <v>39.8388816</v>
+        <v>40.24540080000001</v>
       </c>
       <c r="N100">
-        <v>-33.47221493333333</v>
+        <v>-33.87873413333334</v>
       </c>
       <c r="O100">
-        <v>-7.363887285333333</v>
+        <v>-7.453321509333334</v>
       </c>
       <c r="P100">
-        <v>-26.108327648</v>
+        <v>-26.425412624</v>
       </c>
       <c r="Q100">
-        <v>-22.328327648</v>
+        <v>-22.645412624</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.320712255052298</v>
+        <v>6.595624510104596</v>
       </c>
       <c r="T100">
-        <v>42.68308517647195</v>
+        <v>85.3661703529439</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0351582828235486</v>
+        <v>0.03480314865361377</v>
       </c>
       <c r="W100">
-        <v>0.2275096769102072</v>
+        <v>0.2275934175474779</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1598103764706755</v>
+        <v>0.1581961302436989</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2912737284730491</v>
-      </c>
-      <c r="C101">
-        <v>-116.0702873895661</v>
-      </c>
-      <c r="D101">
-        <v>45.29571261043392</v>
-      </c>
-      <c r="E101">
-        <v>137.076</v>
-      </c>
-      <c r="F101">
-        <v>170.676</v>
-      </c>
-      <c r="G101">
-        <v>9.31</v>
-      </c>
-      <c r="H101">
-        <v>138.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.14666666666667</v>
-      </c>
-      <c r="K101">
-        <v>3.78</v>
-      </c>
-      <c r="L101">
-        <v>6.366666666666666</v>
-      </c>
-      <c r="M101">
-        <v>40.24540080000001</v>
-      </c>
-      <c r="N101">
-        <v>-33.87873413333334</v>
-      </c>
-      <c r="O101">
-        <v>-7.453321509333334</v>
-      </c>
-      <c r="P101">
-        <v>-26.425412624</v>
-      </c>
-      <c r="Q101">
-        <v>-22.645412624</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.595624510104596</v>
-      </c>
-      <c r="T101">
-        <v>85.3661703529439</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03480314865361377</v>
-      </c>
-      <c r="W101">
-        <v>0.2275934175474779</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1581961302436989</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
